--- a/main_code/database.xlsx
+++ b/main_code/database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://changgunguniversity-my.sharepoint.com/personal/b1229046_cgu_edu_tw/Documents/專題/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="471" documentId="11_D31873DEB2784B3F0E0D2040A827BD41A3BCFC82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEA6E9B5-05F4-4AA3-A31B-88A46AD0FBA7}"/>
+  <xr:revisionPtr revIDLastSave="831" documentId="11_D31873DEB2784B3F0E0D2040A827BD41A3BCFC82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9171837-C1E5-4D6E-A285-6B5BFEF36F1A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="712">
   <si>
     <t>ID</t>
   </si>
@@ -497,7 +497,7 @@
     <t>N_018</t>
   </si>
   <si>
-    <t>爸爸</t>
+    <t>爸爸/父親</t>
   </si>
   <si>
     <t>sequence([is_L_shape_RIGHT_HAND == True and dist_HAND_8_FACE_CHEEK_R &lt; 0.05], [is_thumb_up_RIGHT_HAND == True and detect_small_move_outwards_RIGHT_HAND == True])</t>
@@ -506,7 +506,7 @@
     <t>N_019</t>
   </si>
   <si>
-    <t>媽媽</t>
+    <t>媽媽/母親</t>
   </si>
   <si>
     <t>sequence([is_index_pinky_extended_RIGHT_HAND == True and dist_HAND_8_FACE_CHEEK_R &lt; 0.05], [is_pinky_extended_RIGHT_HAND == True and detect_small_move_outwards_RIGHT_HAND == True])</t>
@@ -548,9 +548,6 @@
     <t>is_ring_finger_extended_RIGHT_HAND == True and dist_HAND_16_FACE_CHEEK_R &lt; 0.05 and move_upwards_RIGHT_HAND == True</t>
   </si>
   <si>
-    <t>hand:8 | vector:in_to_out | action:rotate_move</t>
-  </si>
-  <si>
     <t>N_024</t>
   </si>
   <si>
@@ -605,6 +602,9 @@
     <t>嬸嬸</t>
   </si>
   <si>
+    <t>母親+姊(妹)</t>
+  </si>
+  <si>
     <t>N_030</t>
   </si>
   <si>
@@ -620,24 +620,36 @@
     <t>姨丈</t>
   </si>
   <si>
+    <t>父親+姊(妹)</t>
+  </si>
+  <si>
     <t>N_032</t>
   </si>
   <si>
     <t>姑姑</t>
   </si>
   <si>
+    <t>爸爸+姊姊+先生</t>
+  </si>
+  <si>
     <t>N_033</t>
   </si>
   <si>
     <t>姑丈</t>
   </si>
   <si>
+    <t>母親+兄(弟)</t>
+  </si>
+  <si>
     <t>N_034</t>
   </si>
   <si>
     <t>舅舅</t>
   </si>
   <si>
+    <t>媽媽+弟+太太</t>
+  </si>
+  <si>
     <t>N_035</t>
   </si>
   <si>
@@ -650,6 +662,9 @@
     <t>先生/男</t>
   </si>
   <si>
+    <t>sequence([is_thumb_extended_HAND == True, is_fist_HAND == True, dist_HAND_0_POSE_CHEST &lt; 1.15, is_right_front_HAND_0_POSE_CHEST == True], [detect_wave_HAND_horizontal == True, dist_HAND_0_POSE_CHEST &lt; 1.20])</t>
+  </si>
+  <si>
     <t>結婚+女生</t>
   </si>
   <si>
@@ -665,18 +680,492 @@
     <t>夫妻_A/夫婦_A</t>
   </si>
   <si>
+    <t>sequence([is_thumb_extended_LEFT_HAND == True and is_pinky_extended_RIGHT_HAND == True and dist_LEFT_HAND_4_RIGHT_HAND_20 &lt; 0.10], [is_V_shape_HAND == True and vector_align_HAND_PALM_INWARD &gt; 0.7 and detect_wave_HAND_horizontal == True])</t>
+  </si>
+  <si>
     <t>N_039</t>
   </si>
   <si>
     <t>夫妻_B/夫婦_B</t>
   </si>
   <si>
+    <t>sequence([is_thumb_extended_LEFT_HAND == True and is_pinky_extended_RIGHT_HAND == True and dist_LEFT_HAND_4_RIGHT_HAND_20 &lt; 0.10], [move_upwards_RIGHT_HAND == True and move_upwards_LEFT_HAND == True and dist_LEFT_HAND_4_RIGHT_HAND_20 &gt; 0.20])</t>
+  </si>
+  <si>
     <t>N_040</t>
   </si>
   <si>
     <t>女生/女性/小姐</t>
   </si>
   <si>
+    <t>is_pinky_extended_RIGHT_HAND == True and detect_wave_HAND_horizontal == True and dist_HAND_0_POSE_CHEST &lt; 0.90</t>
+  </si>
+  <si>
+    <t>N_041</t>
+  </si>
+  <si>
+    <t>物/東西</t>
+  </si>
+  <si>
+    <t>is_L_shape_RIGHT_HAND == True and palm_facing_down_RIGHT_HAND == True and move_right_RIGHT_HAND == True and detect_index_flap_RIGHT_HAND == True</t>
+  </si>
+  <si>
+    <t>N_042</t>
+  </si>
+  <si>
+    <t>水餃/餃子/包水餃</t>
+  </si>
+  <si>
+    <t>is_pinch_LEFT_HAND == True and palm_facing_up_LEFT_HAND == True and dist_RIGHT_HAND_0_LEFT_HAND_0 &lt; 0.2 and detect_repeating_pinch_RIGHT_HAND == True</t>
+  </si>
+  <si>
+    <t>N_043</t>
+  </si>
+  <si>
+    <t>晚上_A</t>
+  </si>
+  <si>
+    <t>sequence([palm_facing_out_RIGHT_HAND == True and dist_RIGHT_HAND_LEFT_HAND &gt; 0.60], [dist_RIGHT_HAND_LEFT_HAND &lt; 0.20 and dist_RIGHT_HAND_0_POSE_CHEST &lt; 0.50])</t>
+  </si>
+  <si>
+    <t>N_044</t>
+  </si>
+  <si>
+    <t>家_A/屋子/館</t>
+  </si>
+  <si>
+    <t>is_flat_BOTH_HANDS == True and dist_RIGHT_HAND_12_LEFT_HAND_12 &lt; 0.08 and dist_HAND_0_POSE_CHEST &lt; 0.60 and is_static_HAND == True</t>
+  </si>
+  <si>
+    <t>N_045</t>
+  </si>
+  <si>
+    <t>家_B</t>
+  </si>
+  <si>
+    <t>is_thumb_extended_HAND == True and dist_HAND_4_MOUTH &lt; 0.15 and is_static_HAND == True</t>
+  </si>
+  <si>
+    <t>N_046</t>
+  </si>
+  <si>
+    <t>路/道路</t>
+  </si>
+  <si>
+    <t>sequence([is_ILY_shape_HAND == True and is_ILY_shape_LEFT_HAND == True and hands_facing_BOTH_HANDS == True and dist_HAND_0_POSE_CHEST &lt; 0.30], [dist_HAND_0_POSE_CHEST &gt; 0.55])</t>
+  </si>
+  <si>
+    <t>N_047</t>
+  </si>
+  <si>
+    <t>這</t>
+  </si>
+  <si>
+    <t>is_index_pointing_HAND == True and move_downwards_RIGHT_HAND == True and dist_HAND_8_POSE_CHEST &lt; 0.60</t>
+  </si>
+  <si>
+    <t>N_048</t>
+  </si>
+  <si>
+    <t>種類/類別/等等</t>
+  </si>
+  <si>
+    <t>sequence([is_flat_HAND == True and dist_RIGHT_HAND_20_LEFT_HAND_0 &lt; 0.15], [detect_circle_RIGHT_HAND == True and dist_RIGHT_HAND_8_LEFT_HAND_4 &lt; 0.20])</t>
+  </si>
+  <si>
+    <t>N_049</t>
+  </si>
+  <si>
+    <t>老師_S</t>
+  </si>
+  <si>
+    <t>is_L_shape_HAND == True and detect_finger_bend_repeat_HAND_8 == True and dist_HAND_0_POSE_CHEST &lt; 0.60</t>
+  </si>
+  <si>
+    <t>N_050</t>
+  </si>
+  <si>
+    <t>四季</t>
+  </si>
+  <si>
+    <t>sequence([is_index_pointing_HAND == True and dist_RIGHT_HAND_8_LEFT_HAND_0 &lt; 0.25], [detect_circle_RIGHT_HAND == True and dist_RIGHT_HAND_8_LEFT_HAND_0 &lt; 0.30])</t>
+  </si>
+  <si>
+    <t>N_051</t>
+  </si>
+  <si>
+    <t>邊</t>
+  </si>
+  <si>
+    <t>sequence([is_open_BOTH_HANDS == True, palm_facing_down_LEFT_HAND == True, dist_RIGHT_HAND_0_LEFT_ELBOW &lt; 0.2], [dist_RIGHT_HAND_0_LEFT_HAND_0 &lt; 0.15])</t>
+  </si>
+  <si>
+    <t>N_052</t>
+  </si>
+  <si>
+    <t>醫</t>
+  </si>
+  <si>
+    <t>is_open_LEFT_HAND == True and palm_facing_up_LEFT_HAND == True and is_curved_RIGHT_HAND == True and dist_RIGHT_HAND_TIPS_LEFT_HAND_0 &lt; 0.1</t>
+  </si>
+  <si>
+    <t>N_053</t>
+  </si>
+  <si>
+    <t>票/片/券</t>
+  </si>
+  <si>
+    <t>sequence([is_L_shape_BOTH_HANDS == True, dist_RIGHT_HAND_LEFT_HAND &lt; 0.1], [move_apart_horizontally_RIGHT_HAND_LEFT_HAND == True], [move_closer_RIGHT_HAND_LEFT_HAND == True])</t>
+  </si>
+  <si>
+    <t>N_054</t>
+  </si>
+  <si>
+    <t>警察</t>
+  </si>
+  <si>
+    <t>is_C_shape_RIGHT_HAND == True and dist_RIGHT_HAND_4_FACE_FOREHEAD &lt; 0.1</t>
+  </si>
+  <si>
+    <t>N_055</t>
+  </si>
+  <si>
+    <t>車_A_N/巴士</t>
+  </si>
+  <si>
+    <t>is_open_BOTH_HANDS == True and palm_facing_down_LEFT_HAND == True and palm_facing_left_RIGHT_HAND == True and dist_RIGHT_HAND_0_LEFT_HAND_0 &lt; 0.1 and move_alternating_depth_LEFT_HAND == True</t>
+  </si>
+  <si>
+    <t>N_056</t>
+  </si>
+  <si>
+    <t>公</t>
+  </si>
+  <si>
+    <t>is_L_shape_LEFT_HAND == True and fingers_pointing_down_LEFT_HAND == True and is_circle_shape_RIGHT_HAND == True and is_below_RIGHT_HAND_LEFT_HAND == True</t>
+  </si>
+  <si>
+    <t>公+車_A_N</t>
+  </si>
+  <si>
+    <t>N_057</t>
+  </si>
+  <si>
+    <t>公共汽車_A/公車_A</t>
+  </si>
+  <si>
+    <t>N_058</t>
+  </si>
+  <si>
+    <t>公共汽車_B/公車_B</t>
+  </si>
+  <si>
+    <t>is_fist_RIGHT_HAND == True and dist_RIGHT_HAND_0_FACE_SIDE &lt; 0.2 and detect_swipe_RIGHT_HAND_vertical == True</t>
+  </si>
+  <si>
+    <t>N_059</t>
+  </si>
+  <si>
+    <t>地方/處</t>
+  </si>
+  <si>
+    <t>is_claw_RIGHT_HAND == True and move_downwards_RIGHT_HAND == True and dist_RIGHT_HAND_0_POSE_CHEST &lt; 0.3</t>
+  </si>
+  <si>
+    <t>公共汽車_B+地方</t>
+  </si>
+  <si>
+    <t>N_060</t>
+  </si>
+  <si>
+    <t>公車站_A/公車亭_A</t>
+  </si>
+  <si>
+    <t>停車+地方</t>
+  </si>
+  <si>
+    <t>N_061</t>
+  </si>
+  <si>
+    <t>停車場</t>
+  </si>
+  <si>
+    <t>運輸+車_A_N</t>
+  </si>
+  <si>
+    <t>N_062</t>
+  </si>
+  <si>
+    <t>卡車</t>
+  </si>
+  <si>
+    <t>N_063</t>
+  </si>
+  <si>
+    <t>吊車</t>
+  </si>
+  <si>
+    <t>sequence([is_C_shape_LEFT_HAND == True, palm_facing_down_LEFT_HAND == True, is_hook_RIGHT_HAND == True, dist_RIGHT_HAND_0_LEFT_CHEST &lt; 0.2], [move_upwards_RIGHT_HAND == True, move_right_RIGHT_HAND == True])</t>
+  </si>
+  <si>
+    <t>N_064</t>
+  </si>
+  <si>
+    <t>手推車</t>
+  </si>
+  <si>
+    <t>is_fist_BOTH_HANDS == True and palm_facing_down_BOTH_HANDS == True and move_forwards_BOTH_HANDS == True</t>
+  </si>
+  <si>
+    <t>車_A_N+轉</t>
+  </si>
+  <si>
+    <t>N_065</t>
+  </si>
+  <si>
+    <t>接駁車</t>
+  </si>
+  <si>
+    <t>N_066</t>
+  </si>
+  <si>
+    <t>機車/摩托車</t>
+  </si>
+  <si>
+    <t>is_fist_BOTH_HANDS == True and palm_facing_down_BOTH_HANDS == True and detect_wrist_rotation_BOTH_HANDS == True</t>
+  </si>
+  <si>
+    <t>N_067</t>
+  </si>
+  <si>
+    <t>閃光信號車</t>
+  </si>
+  <si>
+    <t>is_C_shape_LEFT_HAND == True and palm_facing_down_LEFT_HAND == True and is_claw_RIGHT_HAND == True and palm_facing_up_RIGHT_HAND == True and detect_wrist_rotation_RIGHT_HAND == True</t>
+  </si>
+  <si>
+    <t>醫+閃光信號車</t>
+  </si>
+  <si>
+    <t>N_068</t>
+  </si>
+  <si>
+    <t>救護車</t>
+  </si>
+  <si>
+    <t>機車+行+證明</t>
+  </si>
+  <si>
+    <t>N_069</t>
+  </si>
+  <si>
+    <t>機車行照</t>
+  </si>
+  <si>
+    <t>機車+證明</t>
+  </si>
+  <si>
+    <t>N_070</t>
+  </si>
+  <si>
+    <t>機車駕照</t>
+  </si>
+  <si>
+    <t>開車+證明</t>
+  </si>
+  <si>
+    <t>N_071</t>
+  </si>
+  <si>
+    <t>汽車駕照</t>
+  </si>
+  <si>
+    <t>N_072</t>
+  </si>
+  <si>
+    <t>火車_N</t>
+  </si>
+  <si>
+    <t>is_open_LEFT_HAND == True and is_U_shape_RIGHT_HAND == True and dist_RIGHT_HAND_0_LEFT_HAND_0 &lt; 0.15 and detect_circle_RIGHT_HAND == True</t>
+  </si>
+  <si>
+    <t>火車_N+票</t>
+  </si>
+  <si>
+    <t>N_073</t>
+  </si>
+  <si>
+    <t>火車票</t>
+  </si>
+  <si>
+    <t>火車_N+地方</t>
+  </si>
+  <si>
+    <t>N_074</t>
+  </si>
+  <si>
+    <t>火車站/車站</t>
+  </si>
+  <si>
+    <t>N_075</t>
+  </si>
+  <si>
+    <t>腳踏車_A/騎腳踏車_A</t>
+  </si>
+  <si>
+    <t>is_fist_BOTH_HANDS == True and detect_alternating_circle_BOTH_HANDS == True</t>
+  </si>
+  <si>
+    <t>N_076</t>
+  </si>
+  <si>
+    <t>計程車</t>
+  </si>
+  <si>
+    <t>is_C_shape_LEFT_HAND == True and palm_facing_down_LEFT_HAND == True and is_index_pointing_RIGHT_HAND == True and dist_RIGHT_HAND_8_LEFT_HAND_0 &lt; 0.1 and detect_swipe_RIGHT_HAND_horizontal == True</t>
+  </si>
+  <si>
+    <t>警察+閃光信號車</t>
+  </si>
+  <si>
+    <t>N_077</t>
+  </si>
+  <si>
+    <t>警車</t>
+  </si>
+  <si>
+    <t>N_078</t>
+  </si>
+  <si>
+    <t>車庫</t>
+  </si>
+  <si>
+    <t>sequence([is_C_shape_RIGHT_HAND == True, palm_facing_down_RIGHT_HAND == True, dist_RIGHT_HAND_0_RIGHT_SHOULDER &lt; 0.2, is_open_LEFT_HAND == True], [move_left_RIGHT_HAND == True, is_below_RIGHT_HAND_LEFT_HAND == True])</t>
+  </si>
+  <si>
+    <t>N_079</t>
+  </si>
+  <si>
+    <t>台北捷運/北捷</t>
+  </si>
+  <si>
+    <t>is_double_hook_BOTH_HANDS == True and palms_facing_each_other == True and move_forwards_BOTH_HANDS == True</t>
+  </si>
+  <si>
+    <t>N_080</t>
+  </si>
+  <si>
+    <t>捷運/地鐵</t>
+  </si>
+  <si>
+    <t>is_V_shape_HAND == True and hands_facing_BOTH_HANDS == True and detect_swipe_HAND_forward == True</t>
+  </si>
+  <si>
+    <t>N_081</t>
+  </si>
+  <si>
+    <t>高雄捷運/高捷</t>
+  </si>
+  <si>
+    <t>is_K_shape_BOTH_HANDS == True and palm_facing_in_BOTH_HANDS == True and dist_RIGHT_HAND_8_LEFT_HAND_8 &lt; 0.1 and move_alternating_depth_BOTH_HANDS == True</t>
+  </si>
+  <si>
+    <t>N_082</t>
+  </si>
+  <si>
+    <t>輕軌電車</t>
+  </si>
+  <si>
+    <t>sequence([is_flat_BOTH_HANDS == True and palm_facing_up_LEFT_HAND == True and detect_tap_HAND == True], [is_flat_RIGHT_HAND == True and dist_RIGHT_HAND_8_LEFT_HAND_0 &lt; 0.15 and detect_swipe_HAND_forward == True])</t>
+  </si>
+  <si>
+    <t>N_083</t>
+  </si>
+  <si>
+    <t>高鐵_A</t>
+  </si>
+  <si>
+    <t>sequence([is_open_RIGHT_HAND == True, palm_facing_in_RIGHT_HAND == True], [move_forwards_RIGHT_HAND == True, is_pinch_RIGHT_HAND == True])</t>
+  </si>
+  <si>
+    <t>高鐵_A+地方</t>
+  </si>
+  <si>
+    <t>N_084</t>
+  </si>
+  <si>
+    <t>高鐵站_A</t>
+  </si>
+  <si>
+    <t>古/古老/古時候</t>
+  </si>
+  <si>
+    <t>N_085</t>
+  </si>
+  <si>
+    <t>飛機</t>
+  </si>
+  <si>
+    <t>is_airplane_shape_RIGHT_HAND == True and move_left_RIGHT_HAND == True and move_forwards_RIGHT_HAND == True</t>
+  </si>
+  <si>
+    <t>角</t>
+  </si>
+  <si>
+    <t>飛機+票</t>
+  </si>
+  <si>
+    <t>N_086</t>
+  </si>
+  <si>
+    <t>機票</t>
+  </si>
+  <si>
+    <t>N_087</t>
+  </si>
+  <si>
+    <t>船/舟</t>
+  </si>
+  <si>
+    <t>is_open_BOTH_HANDS == True and palm_facing_up_BOTH_HANDS == True and dist_RIGHT_HAND_20_LEFT_HAND_20 &lt; 0.05 and move_forwards_BOTH_HANDS == True</t>
+  </si>
+  <si>
+    <t>上告</t>
+  </si>
+  <si>
+    <t>N_088</t>
+  </si>
+  <si>
+    <t>帆船</t>
+  </si>
+  <si>
+    <t>sequence([palm_facing_up_LEFT_HAND == True and is_flat_RIGHT_HAND == True and vector_align_HAND_8_DOWN_AXIS &lt; -0.50], [dist_RIGHT_HAND_8_LEFT_HAND_0 &lt; 0.20 and detect_swipe_HAND_forward == True])</t>
+  </si>
+  <si>
+    <t>不要臉_A</t>
+  </si>
+  <si>
+    <t>習慣_N+差勁</t>
+  </si>
+  <si>
+    <t>壞習慣_A</t>
+  </si>
+  <si>
+    <t>習慣_N+不好_A</t>
+  </si>
+  <si>
+    <t>壞習慣_B</t>
+  </si>
+  <si>
+    <t>棒球_A</t>
+  </si>
+  <si>
+    <t>棒球_B</t>
+  </si>
+  <si>
+    <t>血_A</t>
+  </si>
+  <si>
     <t>V_001</t>
   </si>
   <si>
@@ -686,6 +1175,9 @@
     <t>is_static_HAND == False and palm_facing_in_RIGHT_HAND == True and palm_facing_down_HAND == False and is_open_HAND == False and dist_HAND_0_POSE_CHEST &lt; 1.35</t>
   </si>
   <si>
+    <t>血_B</t>
+  </si>
+  <si>
     <t>V_002</t>
   </si>
   <si>
@@ -695,6 +1187,9 @@
     <t>is_open5_BOTH_HANDS == True and hands_facing_BOTH_HANDS == True and detect_wave_BOTH_HANDS_vertical == True</t>
   </si>
   <si>
+    <t>血型</t>
+  </si>
+  <si>
     <t>V_003</t>
   </si>
   <si>
@@ -702,6 +1197,9 @@
   </si>
   <si>
     <t>is_open_HAND == True and is_thumb_extended_LEFT_HAND == True and dist_START_RIGHT_HAND_0_START_LEFT_HAND_0 &lt; 0.35</t>
+  </si>
+  <si>
+    <t>臉紅</t>
   </si>
   <si>
     <t>V_004</t>
@@ -714,6 +1212,9 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
+    <t>別的/其他/另外/外面</t>
+  </si>
+  <si>
     <t>V_005</t>
   </si>
   <si>
@@ -919,6 +1420,9 @@
     <t>謝謝_B</t>
   </si>
   <si>
+    <t>sequence([is_thumb_extended_HAND == False and is_four_fingers_closed_HAND == True and dist_RIGHT_HAND_LEFT_HAND &lt; 0.20 and dist_HAND_0_POSE_CHEST &lt; 0.80], [detect_swipe_HAND_up == True and dist_HAND_8_FACE_1 &lt; 0.25])</t>
+  </si>
+  <si>
     <t>V_025</t>
   </si>
   <si>
@@ -934,6 +1438,291 @@
     <t>結婚</t>
   </si>
   <si>
+    <t>is_thumb_extended_LEFT_HAND == True and is_pinky_extended_RIGHT_HAND == True and dist_LEFT_HAND_4_RIGHT_HAND_20 &lt; 0.10 and dist_HAND_0_POSE_CHEST &lt; 0.80 and dist_HAND_0_POSE_CHIN &lt; 0.90</t>
+  </si>
+  <si>
+    <t>V_027</t>
+  </si>
+  <si>
+    <t>拿/取</t>
+  </si>
+  <si>
+    <t>sequence([palm_facing_down_HAND == True and is_open_HAND == True], [is_pinch_all_HAND == True])</t>
+  </si>
+  <si>
+    <t>V_028</t>
+  </si>
+  <si>
+    <t>要_S/需要_S</t>
+  </si>
+  <si>
+    <t>sequence([is_V_shape_HAND == True and dist_HAND_0_POSE_CHEST &gt; 0.50], [is_V_shape_HAND == True and dist_HAND_0_POSE_CHEST &lt; 0.25])</t>
+  </si>
+  <si>
+    <t>V_029</t>
+  </si>
+  <si>
+    <t>要_N/需要_N</t>
+  </si>
+  <si>
+    <t>is_pinch_RIGHT_HAND == True and dist_HAND_0_POSE_CHIN &lt; 0.35 and is_static_HAND == True</t>
+  </si>
+  <si>
+    <t>V_030</t>
+  </si>
+  <si>
+    <t>離開</t>
+  </si>
+  <si>
+    <t>sequence([palm_facing_in_RIGHT_HAND == True and is_open_HAND == True], [palm_facing_out_RIGHT_HAND == True])</t>
+  </si>
+  <si>
+    <t>家_A+離開</t>
+  </si>
+  <si>
+    <t>V_031</t>
+  </si>
+  <si>
+    <t>回家_A</t>
+  </si>
+  <si>
+    <t>家_B+離開</t>
+  </si>
+  <si>
+    <t>V_032</t>
+  </si>
+  <si>
+    <t>回家_B</t>
+  </si>
+  <si>
+    <t>V_033</t>
+  </si>
+  <si>
+    <t>旅行/旅遊</t>
+  </si>
+  <si>
+    <t>palm_facing_in_RIGHT_HAND == True and detect_wave_HAND_horizontal == True and dist_HAND_0_POSE_CHIN &lt; 0.40</t>
+  </si>
+  <si>
+    <t>V_034</t>
+  </si>
+  <si>
+    <t>帶</t>
+  </si>
+  <si>
+    <t>sequence([dist_RIGHT_HAND_LEFT_HAND &lt; 0.15 and is_fist_HAND == True], [detect_swipe_HAND_horizontal == True])</t>
+  </si>
+  <si>
+    <t>V_035</t>
+  </si>
+  <si>
+    <t>玩/遊戲</t>
+  </si>
+  <si>
+    <t>is_index_BOTH_HANDS == True and dist_HAND_8_FACE_1 &lt; 0.50 and detect_wave_HAND_horizontal == True</t>
+  </si>
+  <si>
+    <t>V_036</t>
+  </si>
+  <si>
+    <t>新</t>
+  </si>
+  <si>
+    <t>sequence([is_pinch_all_HAND == True and dist_HAND_0_POSE_SHOULDER_R &lt; 0.25], [is_open_HAND == True and vector_align_HAND_PALM_UPWARD == True and detect_swipe_HAND_forward == True])</t>
+  </si>
+  <si>
+    <t>V_037</t>
+  </si>
+  <si>
+    <t>舊_A</t>
+  </si>
+  <si>
+    <t>sequence([vector_align_HAND_PALM_UPWARD == True and dist_HAND_0_POSE_CHEST &lt; 0.50], [is_fist_HAND == True and dist_HAND_0_POSE_SHOULDER_R &lt; 0.25])</t>
+  </si>
+  <si>
+    <t>V_038</t>
+  </si>
+  <si>
+    <t>舊_B</t>
+  </si>
+  <si>
+    <t>is_index_pointing_HAND == True and dist_HAND_8_FACE_CHEEK_R &lt; 0.15 and detect_finger_bend_repeat_HAND_8 == True</t>
+  </si>
+  <si>
+    <t>V_039</t>
+  </si>
+  <si>
+    <t>走/走路/行走</t>
+  </si>
+  <si>
+    <t>is_V_shape_HAND == True and vector_align_HAND_8_DOWN_AXIS &gt; 0.60 and detect_swipe_HAND_horizontal == True</t>
+  </si>
+  <si>
+    <t>V_040</t>
+  </si>
+  <si>
+    <t>知道_N/曉得_N/懂_N</t>
+  </si>
+  <si>
+    <t>palm_facing_in_RIGHT_HAND == True and move_downwards_RIGHT_HAND == True and dist_HAND_0_POSE_CHEST &lt; 0.60</t>
+  </si>
+  <si>
+    <t>V_041</t>
+  </si>
+  <si>
+    <t>知道_S/曉得_S/懂_S/認識_A</t>
+  </si>
+  <si>
+    <t>is_fist_HAND == True and detect_tap_HAND == True and dist_HAND_0_POSE_CHEST &lt; 0.50</t>
+  </si>
+  <si>
+    <t>V_042</t>
+  </si>
+  <si>
+    <t>不認識_A/陌生</t>
+  </si>
+  <si>
+    <t>sequence([is_fingers_bent_HAND == True and is_thumb_extended_HAND == True and dist_HAND_8_FACE_CHEEK_R &lt; 0.15], [is_open_HAND == True and detect_swipe_HAND_outward == True])</t>
+  </si>
+  <si>
+    <t>V_043</t>
+  </si>
+  <si>
+    <t>會_N</t>
+  </si>
+  <si>
+    <t>sequence([dist_RIGHT_HAND_BACK_LEFT_PALM &lt; 0.15], [dist_RIGHT_HAND_BACK_LEFT_PALM &gt; 0.35 and detect_swipe_HAND_outward == True])</t>
+  </si>
+  <si>
+    <t>V_044</t>
+  </si>
+  <si>
+    <t>見</t>
+  </si>
+  <si>
+    <t>is_V_shape_HAND == True and vector_align_HAND_8_CAMERA_AXIS &gt; 0.60 and is_static_HAND == True</t>
+  </si>
+  <si>
+    <t>V_045</t>
+  </si>
+  <si>
+    <t>不行/不能/不肯</t>
+  </si>
+  <si>
+    <t>is_fist_HAND == True and palm_facing_out_RIGHT_HAND == True and detect_wave_HAND_horizontal == True</t>
+  </si>
+  <si>
+    <t>V_046</t>
+  </si>
+  <si>
+    <t>運輸</t>
+  </si>
+  <si>
+    <t>is_thumb_up_RIGHT_HAND == True and is_flat_LEFT_HAND == True and palm_facing_up_LEFT_HAND == True and dist_RIGHT_HAND_0_LEFT_HAND_0 &lt; 0.20 and detect_swipe_HAND_forward == True</t>
+  </si>
+  <si>
+    <t>V_047</t>
+  </si>
+  <si>
+    <t>轉</t>
+  </si>
+  <si>
+    <t>is_index_BOTH_HANDS == True and dist_RIGHT_HAND_8_LEFT_HAND_8 &gt; 0.05 and detect_circle_BOTH_HANDS == True</t>
+  </si>
+  <si>
+    <t>不用拍</t>
+  </si>
+  <si>
+    <t>V_048</t>
+  </si>
+  <si>
+    <t>行</t>
+  </si>
+  <si>
+    <t>is_V_shape_HAND == True and vector_align_HAND_8_DOWN_AXIS &gt; 0.60 and detect_alternate_swing_BOTH_HANDS == True</t>
+  </si>
+  <si>
+    <t>V_049</t>
+  </si>
+  <si>
+    <t>上車/就任/上台</t>
+  </si>
+  <si>
+    <t>sequence([is_thumb_up_RIGHT_HAND == True and dist_RIGHT_HAND_0_POSE_HIP &lt; 0.25], [is_thumb_up_RIGHT_HAND == True and dist_RIGHT_HAND_0_LEFT_HAND_0 &lt; 0.20 and is_above_RIGHT_HAND_LEFT_HAND == True])</t>
+  </si>
+  <si>
+    <t>V_050</t>
+  </si>
+  <si>
+    <t>下車/下台/卸任</t>
+  </si>
+  <si>
+    <t>sequence([is_thumb_up_RIGHT_HAND == True and dist_RIGHT_HAND_0_LEFT_HAND_0 &lt; 0.20 and is_above_RIGHT_HAND_LEFT_HAND == True], [is_thumb_up_RIGHT_HAND == True and dist_RIGHT_HAND_0_POSE_HIP &lt; 0.25])</t>
+  </si>
+  <si>
+    <t>V_051</t>
+  </si>
+  <si>
+    <t>停車</t>
+  </si>
+  <si>
+    <t>is_four_fingers_closed_HAND == True and palm_facing_down_HAND == True and dist_RIGHT_HAND_0_LEFT_HAND_0 &lt; 0.15 and palm_facing_up_LEFT_HAND == True</t>
+  </si>
+  <si>
+    <t>V_052</t>
+  </si>
+  <si>
+    <t>塞車</t>
+  </si>
+  <si>
+    <t>sequence([is_four_fingers_closed_HAND == True and palm_facing_down_HAND == True and is_static_LEFT_HAND == True], [detect_small_move_HAND_z == True and is_four_fingers_closed_BOTH_HANDS == True])</t>
+  </si>
+  <si>
+    <t>V_053</t>
+  </si>
+  <si>
+    <t>煞車_A</t>
+  </si>
+  <si>
+    <t>sequence([is_open_HAND == True and dist_HAND_START_FACE_EYE &lt; 0.40], [move_downwards_RIGHT_HAND == True and is_flat_HAND == True])</t>
+  </si>
+  <si>
+    <t>V_054</t>
+  </si>
+  <si>
+    <t>車禍_A</t>
+  </si>
+  <si>
+    <t>sequence([is_four_fingers_closed_HAND == True and palm_facing_down_HAND == True and is_four_fingers_closed_BOTH_HANDS == True and dist_RIGHT_HAND_LEFT_HAND &lt; 0.20], [move_apart_horizontally_RIGHT_HAND_LEFT_HAND == True and hands_facing_BOTH_HANDS == True])</t>
+  </si>
+  <si>
+    <t>V_055</t>
+  </si>
+  <si>
+    <t>開車/駕駛</t>
+  </si>
+  <si>
+    <t>is_fist_BOTH_HANDS == True and detect_alternate_swing_BOTH_HANDS == True</t>
+  </si>
+  <si>
+    <t>V_056</t>
+  </si>
+  <si>
+    <t>飆車_A</t>
+  </si>
+  <si>
+    <t>is_fist_BOTH_HANDS == True and detect_alternate_swing_BOTH_HANDS == True and detect_body_sway_large_amplitude == True</t>
+  </si>
+  <si>
+    <t>V_057</t>
+  </si>
+  <si>
+    <t>划船</t>
+  </si>
+  <si>
+    <t>is_fist_BOTH_HANDS == True and detect_circle_BOTH_HANDS == True and move_backwards_BOTH_HANDS == True</t>
+  </si>
+  <si>
     <t>A_001</t>
   </si>
   <si>
@@ -952,7 +1741,7 @@
     <t>生氣_A/火大/憤怒</t>
   </si>
   <si>
-    <t>sequence([is_index_pointing_HAND == True, vector_align_HAND_out &gt; 0.70, dist_HAND_8_FACE_EAR &lt; 0.20], [is_index_pointing_HAND == True, dist_HAND_8_FACE_1 &gt; 0.30])</t>
+    <t>sequence([is_index_pointing_HAND == True, dist_HAND_8_LEFT_EAR &lt; 0.75, palm_facing_in_RIGHT_HAND == True], [is_index_pointing_HAND == True, dist_HAND_8_FACE_1 &gt; 1.10, move_upwards_RIGHT_HAND == True])</t>
   </si>
   <si>
     <t>A_003</t>
@@ -1009,7 +1798,7 @@
     <t>呼~</t>
   </si>
   <si>
-    <t>sequence([is_flat_HAND == True, vector_align_HAND_PALM_DOWNWARD &gt; 0.70, dist_HAND_8_FACE_TEMPLE &lt; 0.10], [is_flat_HAND == True, dist_HAND_8_FACE_EAR &lt; 0.10, detect_swipe_HAND_down == True])</t>
+    <t>sequence([dist_HAND_8_LEFT_EAR &lt; 0.20, palm_facing_down_HAND == True, palm_facing_in_RIGHT_HAND == True], [move_downwards_RIGHT_HAND == True, dist_HAND_8_LEFT_EAR &gt; 0.45])</t>
   </si>
   <si>
     <t>A_008</t>
@@ -1285,7 +2074,7 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>sequence([is_above_RIGHT_HAND_LEFT_HAND == True and palm_facing_down_HAND == True and dist_HAND_0_POSE_CHEST &lt; 1.30 and is_index_pointing_HAND == False], [move_apart_horizontally_RIGHT_HAND_LEFT_HAND == True and palm_facing_down_HAND == True and is_index_pointing_HAND == False])</t>
+    <t>sequence([is_four_fingers_closed_HAND == True, palm_facing_down_HAND == True, dist_HAND_0_POSE_CHEST &lt; 1.05, is_right_front_HAND_0_POSE_CHEST == True], [detect_swipe_HAND_horizontal == True, move_downwards_RIGHT_HAND == True, dist_HAND_0_POSE_SHOULDER_R &gt; 1.30])</t>
   </si>
   <si>
     <t>A_024</t>
@@ -1330,64 +2119,160 @@
     <t>A_025</t>
   </si>
   <si>
+    <t>好_B</t>
+  </si>
+  <si>
+    <t>A_026</t>
+  </si>
+  <si>
     <t>一樣</t>
   </si>
   <si>
-    <t>A_026</t>
+    <t>A_027</t>
   </si>
   <si>
     <t>不一樣/不同</t>
   </si>
   <si>
+    <t>A_028</t>
+  </si>
+  <si>
+    <t>孤獨_A</t>
+  </si>
+  <si>
+    <t>A_029</t>
+  </si>
+  <si>
+    <t>小心/注意</t>
+  </si>
+  <si>
+    <t>A_030</t>
+  </si>
+  <si>
+    <t>不小心_A/不注意</t>
+  </si>
+  <si>
+    <t>A_031</t>
+  </si>
+  <si>
+    <t>貴_A</t>
+  </si>
+  <si>
+    <t>A_032</t>
+  </si>
+  <si>
+    <t>便宜_A</t>
+  </si>
+  <si>
+    <t>E_001</t>
+  </si>
+  <si>
+    <t>一</t>
+  </si>
+  <si>
+    <t>E_002</t>
+  </si>
+  <si>
+    <t>二</t>
+  </si>
+  <si>
+    <t>E_003</t>
+  </si>
+  <si>
+    <t>三</t>
+  </si>
+  <si>
+    <t>E_004</t>
+  </si>
+  <si>
+    <t>四</t>
+  </si>
+  <si>
+    <t>E_005</t>
+  </si>
+  <si>
+    <t>五</t>
+  </si>
+  <si>
+    <t>E_006</t>
+  </si>
+  <si>
+    <t>六</t>
+  </si>
+  <si>
+    <t>E_007</t>
+  </si>
+  <si>
+    <t>七</t>
+  </si>
+  <si>
+    <t>E_008</t>
+  </si>
+  <si>
+    <t>八</t>
+  </si>
+  <si>
+    <t>E_009</t>
+  </si>
+  <si>
+    <t>九</t>
+  </si>
+  <si>
+    <t>E_010</t>
+  </si>
+  <si>
+    <t>十</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>E_011</t>
+  </si>
+  <si>
+    <t>星期一/禮拜一/週一</t>
+  </si>
+  <si>
+    <t>E_012</t>
+  </si>
+  <si>
+    <t>星期二/禮拜二/週二</t>
+  </si>
+  <si>
+    <t>E_013</t>
+  </si>
+  <si>
+    <t>星期三/禮拜三/週三</t>
+  </si>
+  <si>
+    <t>E_014</t>
+  </si>
+  <si>
+    <t>星期四/禮拜四/週四</t>
+  </si>
+  <si>
+    <t>E_015</t>
+  </si>
+  <si>
+    <t>星期五/禮拜五/週五</t>
+  </si>
+  <si>
+    <t>E_016</t>
+  </si>
+  <si>
+    <t>星期六/禮拜六/週六</t>
+  </si>
+  <si>
+    <t>E_017</t>
+  </si>
+  <si>
+    <t>星期日/禮拜日/週日</t>
+  </si>
+  <si>
     <t>C_001</t>
   </si>
   <si>
     <t>除非</t>
-  </si>
-  <si>
-    <t>古/古老/古時候</t>
-  </si>
-  <si>
-    <t>角</t>
-  </si>
-  <si>
-    <t>上告</t>
-  </si>
-  <si>
-    <t>不要臉_A</t>
-  </si>
-  <si>
-    <t>習慣_N+差勁</t>
-  </si>
-  <si>
-    <t>壞習慣_A</t>
-  </si>
-  <si>
-    <t>習慣_N+不好_A</t>
-  </si>
-  <si>
-    <t>壞習慣_B</t>
-  </si>
-  <si>
-    <t>棒球_A</t>
-  </si>
-  <si>
-    <t>棒球_B</t>
-  </si>
-  <si>
-    <t>血_A</t>
-  </si>
-  <si>
-    <t>血_B</t>
-  </si>
-  <si>
-    <t>血型</t>
-  </si>
-  <si>
-    <t>臉紅</t>
-  </si>
-  <si>
-    <t>別的/其他/另外/外面</t>
   </si>
   <si>
     <t>index+nose(point in)+static</t>
@@ -1576,6 +2461,9 @@
   <si>
     <t>is_thumb_up_LEFT_HAND == True and is_flat_RIGHT_HAND == True and dist_RIGHT_HAND_LEFT_THUMB &lt; 0.05 and detect_tap_RIGHT_HAND == True</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand:8 | vector:in_to_out | action:rotate_move</t>
   </si>
   <si>
     <t>謝謝</t>
@@ -1595,7 +2483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1686,6 +2574,19 @@
       <name val="Google Sans Flex"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF212529"/>
+      <name val="System-Ui"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF212529"/>
+      <name val="System-Ui"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1707,7 +2608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1740,6 +2641,15 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1956,7 +2866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N1000"/>
+  <dimension ref="A1:Q1000"/>
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.375" customWidth="1"/>
@@ -2607,75 +3517,73 @@
       <c r="G36" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="H36" s="1"/>
     </row>
     <row r="37" spans="1:14" ht="16.5" customHeight="1">
       <c r="B37" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" t="s">
         <v>130</v>
-      </c>
-      <c r="C37" t="s">
-        <v>131</v>
       </c>
       <c r="D37" s="1">
         <v>2</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="16.5" customHeight="1">
       <c r="B38" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" t="s">
         <v>133</v>
-      </c>
-      <c r="C38" t="s">
-        <v>134</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="16.5" customHeight="1">
       <c r="B39" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" t="s">
         <v>136</v>
-      </c>
-      <c r="C39" t="s">
-        <v>137</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="16.5" customHeight="1">
       <c r="B40" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" t="s">
         <v>139</v>
-      </c>
-      <c r="C40" t="s">
-        <v>140</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="16.5" customHeight="1">
       <c r="A41" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" t="s">
         <v>143</v>
-      </c>
-      <c r="C41" t="s">
-        <v>144</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
@@ -2683,19 +3591,22 @@
     </row>
     <row r="42" spans="1:14" ht="16.5" customHeight="1">
       <c r="A42" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" t="s">
         <v>146</v>
-      </c>
-      <c r="C42" t="s">
-        <v>147</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A43" t="s">
+        <v>147</v>
+      </c>
       <c r="B43" s="1" t="s">
         <v>148</v>
       </c>
@@ -2721,44 +3632,56 @@
       </c>
     </row>
     <row r="45" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A45" s="13" t="s">
+        <v>153</v>
+      </c>
       <c r="B45" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A46" t="s">
+        <v>156</v>
+      </c>
       <c r="B46" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C46" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D46" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A47" s="12" t="s">
+        <v>159</v>
+      </c>
       <c r="B47" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D47" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A48" s="13" t="s">
+        <v>162</v>
+      </c>
       <c r="B48" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C48" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
@@ -2766,24 +3689,27 @@
     </row>
     <row r="49" spans="1:7" ht="16.5" customHeight="1">
       <c r="B49" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
       </c>
+      <c r="G49" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="50" spans="1:7" ht="16.5" customHeight="1">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C50" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D50" s="1">
         <v>2</v>
@@ -2791,1134 +3717,2479 @@
     </row>
     <row r="51" spans="1:7" ht="16.5" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C51" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D51" s="1">
         <v>2</v>
       </c>
+      <c r="G51" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="52" spans="1:7" ht="16.5" customHeight="1">
       <c r="B52" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C52" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D52" s="1">
         <v>2</v>
       </c>
+      <c r="G52" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="53" spans="1:7" ht="16.5" customHeight="1">
       <c r="B53" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C53" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D53" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="16.5" customHeight="1"/>
+      <c r="G53" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B54" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C54" t="s">
+        <v>181</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2</v>
+      </c>
+      <c r="G54" t="s">
+        <v>182</v>
+      </c>
+    </row>
     <row r="55" spans="1:7" ht="16.5" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>173</v>
+        <v>183</v>
+      </c>
+      <c r="C55" t="s">
+        <v>184</v>
       </c>
       <c r="D55" s="1">
-        <v>3</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>174</v>
+        <v>2</v>
+      </c>
+      <c r="G55" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16.5" customHeight="1">
       <c r="B56" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>176</v>
+        <v>186</v>
+      </c>
+      <c r="C56" t="s">
+        <v>187</v>
       </c>
       <c r="D56" s="1">
-        <v>3</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>177</v>
+        <v>2</v>
+      </c>
+      <c r="G56" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1">
       <c r="B57" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>179</v>
+        <v>189</v>
+      </c>
+      <c r="C57" t="s">
+        <v>190</v>
       </c>
       <c r="D57" s="1">
-        <v>3</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>180</v>
+        <v>2</v>
+      </c>
+      <c r="G57" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="16.5" customHeight="1">
       <c r="B58" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>182</v>
+        <v>192</v>
+      </c>
+      <c r="C58" t="s">
+        <v>193</v>
       </c>
       <c r="D58" s="1">
-        <v>3</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>183</v>
+        <v>2</v>
+      </c>
+      <c r="G58" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="16.5" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>185</v>
+        <v>195</v>
+      </c>
+      <c r="C59" t="s">
+        <v>196</v>
       </c>
       <c r="D59" s="1">
-        <v>3</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>186</v>
+        <v>2</v>
+      </c>
+      <c r="G59" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="16.5" customHeight="1">
       <c r="B60" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>188</v>
+        <v>198</v>
+      </c>
+      <c r="C60" t="s">
+        <v>199</v>
       </c>
       <c r="D60" s="1">
-        <v>3</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>190</v>
+        <v>2</v>
+      </c>
+      <c r="G60" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="16.5" customHeight="1">
       <c r="B61" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>192</v>
+        <v>201</v>
+      </c>
+      <c r="C61" t="s">
+        <v>202</v>
       </c>
       <c r="D61" s="1">
-        <v>3</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>193</v>
+        <v>2</v>
+      </c>
+      <c r="G61" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="16.5" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
+      </c>
+      <c r="C62" t="s">
+        <v>205</v>
       </c>
       <c r="D62" s="1">
-        <v>3</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>196</v>
+        <v>2</v>
+      </c>
+      <c r="G62" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="16.5" customHeight="1">
       <c r="B63" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>198</v>
+        <v>207</v>
+      </c>
+      <c r="C63" t="s">
+        <v>208</v>
       </c>
       <c r="D63" s="1">
-        <v>3</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>199</v>
+        <v>2</v>
+      </c>
+      <c r="G63" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="16.5" customHeight="1">
       <c r="B64" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>201</v>
+        <v>210</v>
+      </c>
+      <c r="C64" t="s">
+        <v>211</v>
       </c>
       <c r="D64" s="1">
+        <v>2</v>
+      </c>
+      <c r="G64" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B65" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C65" t="s">
+        <v>214</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2</v>
+      </c>
+      <c r="G65" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B66" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C66" t="s">
+        <v>217</v>
+      </c>
+      <c r="D66" s="1">
+        <v>2</v>
+      </c>
+      <c r="G66" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B67" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C67" t="s">
+        <v>220</v>
+      </c>
+      <c r="D67" s="1">
+        <v>2</v>
+      </c>
+      <c r="G67" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B68" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C68" t="s">
+        <v>223</v>
+      </c>
+      <c r="D68" s="1">
+        <v>2</v>
+      </c>
+      <c r="G68" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B69" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C69" t="s">
+        <v>226</v>
+      </c>
+      <c r="D69" s="1">
+        <v>2</v>
+      </c>
+      <c r="G69" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A70" t="s">
+        <v>228</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C70" t="s">
+        <v>230</v>
+      </c>
+      <c r="D70" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B71" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C71" t="s">
+        <v>232</v>
+      </c>
+      <c r="D71" s="1">
+        <v>2</v>
+      </c>
+      <c r="G71" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B72" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C72" t="s">
+        <v>235</v>
+      </c>
+      <c r="D72" s="1">
+        <v>2</v>
+      </c>
+      <c r="G72" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A73" t="s">
+        <v>237</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C73" t="s">
+        <v>239</v>
+      </c>
+      <c r="D73" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A74" t="s">
+        <v>240</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C74" t="s">
+        <v>242</v>
+      </c>
+      <c r="D74" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A75" t="s">
+        <v>243</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C75" t="s">
+        <v>245</v>
+      </c>
+      <c r="D75" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B76" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C76" t="s">
+        <v>247</v>
+      </c>
+      <c r="D76" s="1">
+        <v>2</v>
+      </c>
+      <c r="G76" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B77" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C77" t="s">
+        <v>250</v>
+      </c>
+      <c r="D77" s="1">
+        <v>2</v>
+      </c>
+      <c r="G77" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A78" t="s">
+        <v>252</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C78" t="s">
+        <v>254</v>
+      </c>
+      <c r="D78" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B79" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C79" t="s">
+        <v>256</v>
+      </c>
+      <c r="D79" s="1">
+        <v>2</v>
+      </c>
+      <c r="G79" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B80" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C80" t="s">
+        <v>259</v>
+      </c>
+      <c r="D80" s="1">
+        <v>2</v>
+      </c>
+      <c r="G80" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A81" t="s">
+        <v>261</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C81" t="s">
+        <v>263</v>
+      </c>
+      <c r="D81" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A82" t="s">
+        <v>264</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="D82" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A83" t="s">
+        <v>267</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C83" t="s">
+        <v>269</v>
+      </c>
+      <c r="D83" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A84" t="s">
+        <v>270</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C84" t="s">
+        <v>272</v>
+      </c>
+      <c r="D84" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B85" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C85" t="s">
+        <v>274</v>
+      </c>
+      <c r="D85" s="1">
+        <v>2</v>
+      </c>
+      <c r="G85" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A86" t="s">
+        <v>276</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C86" t="s">
+        <v>278</v>
+      </c>
+      <c r="D86" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A87" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C87" t="s">
+        <v>281</v>
+      </c>
+      <c r="D87" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B88" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C88" t="s">
+        <v>283</v>
+      </c>
+      <c r="D88" s="1">
+        <v>2</v>
+      </c>
+      <c r="G88" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B89" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C89" t="s">
+        <v>286</v>
+      </c>
+      <c r="D89" s="1">
+        <v>2</v>
+      </c>
+      <c r="G89" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A90" t="s">
+        <v>288</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C90" t="s">
+        <v>290</v>
+      </c>
+      <c r="D90" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B91" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C91" t="s">
+        <v>292</v>
+      </c>
+      <c r="D91" s="1">
+        <v>2</v>
+      </c>
+      <c r="G91" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B92" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C92" t="s">
+        <v>295</v>
+      </c>
+      <c r="D92" s="1">
+        <v>2</v>
+      </c>
+      <c r="G92" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B93" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C93" t="s">
+        <v>298</v>
+      </c>
+      <c r="D93" s="1">
+        <v>2</v>
+      </c>
+      <c r="G93" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B94" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C94" t="s">
+        <v>301</v>
+      </c>
+      <c r="D94" s="1">
+        <v>2</v>
+      </c>
+      <c r="G94" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B95" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="D95" s="1">
+        <v>2</v>
+      </c>
+      <c r="G95" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B96" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C96" t="s">
+        <v>307</v>
+      </c>
+      <c r="D96" s="1">
+        <v>2</v>
+      </c>
+      <c r="G96" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A97" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C97" t="s">
+        <v>311</v>
+      </c>
+      <c r="D97" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q97" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B98" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C98" t="s">
+        <v>314</v>
+      </c>
+      <c r="D98" s="1">
+        <v>2</v>
+      </c>
+      <c r="G98" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q98" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A99" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C99" t="s">
+        <v>319</v>
+      </c>
+      <c r="D99" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q99" s="1"/>
+    </row>
+    <row r="100" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B100" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C100" t="s">
+        <v>321</v>
+      </c>
+      <c r="D100" s="1">
+        <v>2</v>
+      </c>
+      <c r="G100" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q100" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B101" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C101" t="s">
+        <v>325</v>
+      </c>
+      <c r="D101" s="1">
+        <v>2</v>
+      </c>
+      <c r="G101" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q101" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="16.5" customHeight="1">
+      <c r="O102" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q102" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" ht="16.5" customHeight="1">
+      <c r="O103" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q103" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="16.5" customHeight="1">
+      <c r="Q104" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" ht="16.5" customHeight="1">
+      <c r="Q105" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="16.5" customHeight="1">
+      <c r="Q106" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B107" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D107" s="1">
         <v>3</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E107" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q107" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B108" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D108" s="1">
+        <v>3</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q108" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B109" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D109" s="1">
+        <v>3</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q109" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B110" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D110" s="1">
+        <v>3</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q110" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B111" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D111" s="1">
+        <v>3</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B65" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D65" s="1">
+      <c r="G111" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B112" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D112" s="1">
         <v>3</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E112" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B113" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D113" s="1">
+        <v>3</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B114" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D114" s="1">
+        <v>3</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B115" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D115" s="1">
+        <v>3</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="66" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B66" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D66" s="1">
+      <c r="G115" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B116" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D116" s="1">
         <v>3</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B67" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D67" s="1">
+      <c r="G116" s="5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B117" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D117" s="1">
         <v>3</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E117" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B118" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D118" s="1">
+        <v>3</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B119" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D119" s="1">
+        <v>3</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="68" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B68" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D68" s="1">
+      <c r="F119" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B120" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D120" s="1">
         <v>3</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="69" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B69" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D69" s="1">
+      <c r="G120" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B121" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D121" s="1">
         <v>3</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E121" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G69" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B70" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D70" s="1">
+      <c r="G121" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B122" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D122" s="1">
         <v>3</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E122" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G70" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="71" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B71" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D71" s="1">
+      <c r="F122" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="G122" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B123" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D123" s="1">
         <v>3</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G71" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B72" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D72" s="1">
+      <c r="G123" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B124" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D124" s="1">
         <v>3</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E124" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="G72" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B73" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D73" s="1">
+      <c r="F124" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G124" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B125" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D125" s="1">
         <v>3</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E125" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G73" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="74" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B74" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D74" s="1">
+      <c r="F125" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G125" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B126" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D126" s="1">
         <v>3</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E126" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G74" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="75" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B75" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D75" s="1">
+      <c r="F126" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="G126" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B127" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D127" s="1">
         <v>3</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E127" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G75" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B76" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D76" s="1">
+      <c r="G127" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B128" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D128" s="1">
         <v>3</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G76" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="77" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B77" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D77" s="1">
+      <c r="G128" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B129" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D129" s="1">
         <v>3</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E129" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G77" s="9" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="78" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B78" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D78">
+      <c r="G129" s="9" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B130" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D130">
         <v>3</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E130" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="79" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B79" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C79" t="s">
-        <v>250</v>
-      </c>
-      <c r="D79">
+      <c r="G130" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B131" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C131" t="s">
+        <v>418</v>
+      </c>
+      <c r="D131">
         <v>3</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E131" t="s">
         <v>8</v>
       </c>
-      <c r="G79" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="80" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B80" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C80" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7" ht="16.5" customHeight="1"/>
-    <row r="82" spans="2:7" ht="16.5" customHeight="1"/>
-    <row r="83" spans="2:7" ht="16.5" customHeight="1"/>
-    <row r="84" spans="2:7" ht="16.5" customHeight="1"/>
-    <row r="85" spans="2:7" ht="16.5" customHeight="1"/>
-    <row r="86" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B86" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D86" s="1">
+      <c r="G131" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B132" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C132" t="s">
+        <v>421</v>
+      </c>
+      <c r="D132">
+        <v>3</v>
+      </c>
+      <c r="G132" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B133" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C133" t="s">
+        <v>424</v>
+      </c>
+      <c r="D133">
+        <v>3</v>
+      </c>
+      <c r="G133" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B134" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C134" t="s">
+        <v>427</v>
+      </c>
+      <c r="D134">
+        <v>3</v>
+      </c>
+      <c r="G134" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B135" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C135" t="s">
+        <v>430</v>
+      </c>
+      <c r="D135">
+        <v>3</v>
+      </c>
+      <c r="G135" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B136" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C136" t="s">
+        <v>433</v>
+      </c>
+      <c r="D136">
+        <v>3</v>
+      </c>
+      <c r="G136" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A137" t="s">
+        <v>435</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C137" t="s">
+        <v>437</v>
+      </c>
+      <c r="D137">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A138" t="s">
+        <v>438</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C138" t="s">
+        <v>440</v>
+      </c>
+      <c r="D138">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B139" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C139" t="s">
+        <v>442</v>
+      </c>
+      <c r="D139">
+        <v>3</v>
+      </c>
+      <c r="G139" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B140" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C140" t="s">
+        <v>445</v>
+      </c>
+      <c r="D140">
+        <v>3</v>
+      </c>
+      <c r="G140" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B141" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C141" t="s">
+        <v>448</v>
+      </c>
+      <c r="D141">
+        <v>3</v>
+      </c>
+      <c r="G141" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B142" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C142" t="s">
+        <v>451</v>
+      </c>
+      <c r="D142">
+        <v>3</v>
+      </c>
+      <c r="G142" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B143" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C143" t="s">
+        <v>454</v>
+      </c>
+      <c r="D143">
+        <v>3</v>
+      </c>
+      <c r="G143" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B144" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C144" t="s">
+        <v>457</v>
+      </c>
+      <c r="D144">
+        <v>3</v>
+      </c>
+      <c r="G144" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B145" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C145" t="s">
+        <v>460</v>
+      </c>
+      <c r="D145">
+        <v>3</v>
+      </c>
+      <c r="G145" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B146" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C146" t="s">
+        <v>463</v>
+      </c>
+      <c r="D146">
+        <v>3</v>
+      </c>
+      <c r="G146" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B147" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C147" t="s">
+        <v>466</v>
+      </c>
+      <c r="D147">
+        <v>3</v>
+      </c>
+      <c r="G147" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B148" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C148" t="s">
+        <v>469</v>
+      </c>
+      <c r="D148">
+        <v>3</v>
+      </c>
+      <c r="G148" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B149" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C149" t="s">
+        <v>472</v>
+      </c>
+      <c r="D149">
+        <v>3</v>
+      </c>
+      <c r="G149" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B150" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C150" t="s">
+        <v>475</v>
+      </c>
+      <c r="D150">
+        <v>3</v>
+      </c>
+      <c r="G150" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B151" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C151" t="s">
+        <v>478</v>
+      </c>
+      <c r="D151">
+        <v>3</v>
+      </c>
+      <c r="G151" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B152" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C152" t="s">
+        <v>481</v>
+      </c>
+      <c r="D152">
+        <v>3</v>
+      </c>
+      <c r="G152" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B153" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C153" t="s">
+        <v>484</v>
+      </c>
+      <c r="D153">
+        <v>3</v>
+      </c>
+      <c r="G153" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A154" t="s">
+        <v>486</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C154" t="s">
+        <v>488</v>
+      </c>
+      <c r="D154">
+        <v>3</v>
+      </c>
+      <c r="G154" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B155" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C155" t="s">
+        <v>491</v>
+      </c>
+      <c r="D155">
+        <v>3</v>
+      </c>
+      <c r="G155" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B156" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C156" t="s">
+        <v>494</v>
+      </c>
+      <c r="D156">
+        <v>3</v>
+      </c>
+      <c r="G156" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B157" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C157" t="s">
+        <v>497</v>
+      </c>
+      <c r="D157">
+        <v>3</v>
+      </c>
+      <c r="G157" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B158" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C158" t="s">
+        <v>500</v>
+      </c>
+      <c r="D158">
+        <v>3</v>
+      </c>
+      <c r="G158" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B159" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C159" t="s">
+        <v>503</v>
+      </c>
+      <c r="D159">
+        <v>3</v>
+      </c>
+      <c r="G159" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="16.5" customHeight="1">
+      <c r="B160" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C160" t="s">
+        <v>506</v>
+      </c>
+      <c r="D160">
+        <v>3</v>
+      </c>
+      <c r="G160" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B161" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C161" t="s">
+        <v>509</v>
+      </c>
+      <c r="D161">
+        <v>3</v>
+      </c>
+      <c r="G161" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="162" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B162" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C162" t="s">
+        <v>512</v>
+      </c>
+      <c r="D162">
+        <v>3</v>
+      </c>
+      <c r="G162" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="163" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B163" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C163" t="s">
+        <v>515</v>
+      </c>
+      <c r="D163">
+        <v>3</v>
+      </c>
+      <c r="G163" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="164" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="165" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="166" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="167" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="168" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="169" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="170" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="171" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B171" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D171" s="1">
         <v>4</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E171" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G86" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B87" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D87" s="1">
+      <c r="F171" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="G171" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="172" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B172" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D172" s="1">
         <v>4</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E172" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G87" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B88" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D88" s="1">
+      <c r="F172" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="G172" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="173" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B173" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D173" s="1">
         <v>4</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E173" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="G88" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B89" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D89" s="1">
+      <c r="F173" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="G173" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="174" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B174" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D174" s="1">
         <v>4</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E174" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G89" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B90" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D90" s="1">
+      <c r="G174" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="175" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B175" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D175" s="1">
         <v>4</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E175" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="G90" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B91" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D91" s="1">
+      <c r="F175" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="G175" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="176" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B176" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D176" s="1">
         <v>4</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E176" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="G91" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B92" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D92" s="1">
+      <c r="F176" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="G176" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="177" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B177" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D177" s="1">
         <v>4</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E177" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F92" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="G92" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B93" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D93" s="1">
+      <c r="F177" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G177" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="178" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B178" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D178" s="1">
         <v>4</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E178" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F93" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G93" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B94" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D94" s="1">
+      <c r="F178" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="G178" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="179" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B179" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D179" s="1">
         <v>4</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E179" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G94" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B95" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D95" s="1">
+      <c r="G179" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="180" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B180" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D180" s="1">
         <v>4</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E180" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G95" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B96" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D96" s="1">
+      <c r="G180" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="181" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B181" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D181" s="1">
         <v>4</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E181" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G96" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B97" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D97" s="1">
+      <c r="G181" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="182" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B182" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D182" s="1">
         <v>4</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E182" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G97" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B98" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D98" s="1">
+      <c r="G182" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="183" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B183" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D183" s="1">
         <v>4</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E183" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F98" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G98" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B99" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="D99" s="1">
+      <c r="F183" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="G183" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="184" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B184" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D184" s="1">
         <v>4</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E184" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G99" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B100" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D100" s="1">
+      <c r="F184" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="G184" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="185" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B185" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="D185" s="1">
         <v>4</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E185" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G100" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B101" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="D101" s="1">
+      <c r="G185" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="186" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B186" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D186" s="1">
         <v>4</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E186" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G101" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B102" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="D102" s="1">
+      <c r="G186" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="187" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B187" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D187" s="1">
         <v>4</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E187" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G102" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B103" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="D103" s="1">
+      <c r="G187" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="188" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B188" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="D188" s="1">
         <v>4</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E188" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G103" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B104" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D104" s="1">
+      <c r="G188" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="189" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B189" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D189" s="1">
         <v>4</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E189" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B105" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="D105" s="1">
+    <row r="190" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B190" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D190" s="1">
         <v>4</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E190" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B106" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="D106" s="1">
+    <row r="191" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B191" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D191" s="1">
         <v>4</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E191" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B107" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D107" s="1">
+    <row r="192" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B192" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D192" s="1">
         <v>4</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E192" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B108" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D108" s="1">
+    <row r="193" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B193" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="D193" s="1">
         <v>4</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E193" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G108" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B109" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D109" s="1">
+      <c r="G193" s="5" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="194" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B194" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="D194" s="1">
         <v>4</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E194" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G109" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B110" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C110" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B111" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C111" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7" ht="16.5" customHeight="1"/>
-    <row r="113" spans="1:5" ht="16.5" customHeight="1">
-      <c r="B113" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D113" s="1">
+      <c r="G194" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="195" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B195" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C195" t="s">
+        <v>594</v>
+      </c>
+      <c r="D195" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B196" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C196" t="s">
+        <v>596</v>
+      </c>
+      <c r="D196" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B197" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C197" t="s">
+        <v>598</v>
+      </c>
+      <c r="D197" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B198" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C198" t="s">
+        <v>600</v>
+      </c>
+      <c r="D198" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B199" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C199" t="s">
+        <v>602</v>
+      </c>
+      <c r="D199" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B200" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C200" t="s">
+        <v>604</v>
+      </c>
+      <c r="D200" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B201" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C201" t="s">
+        <v>606</v>
+      </c>
+      <c r="D201" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B202" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C202" t="s">
+        <v>608</v>
+      </c>
+      <c r="D202" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="204" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="205" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="206" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="207" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="208" spans="2:7" ht="16.5" customHeight="1"/>
+    <row r="209" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="210" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="211" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B211" t="s">
+        <v>609</v>
+      </c>
+      <c r="C211" t="s">
+        <v>610</v>
+      </c>
+      <c r="D211">
+        <v>5</v>
+      </c>
+      <c r="E211" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B212" t="s">
+        <v>611</v>
+      </c>
+      <c r="C212" t="s">
+        <v>612</v>
+      </c>
+      <c r="D212">
+        <v>5</v>
+      </c>
+      <c r="E212" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B213" t="s">
+        <v>613</v>
+      </c>
+      <c r="C213" t="s">
+        <v>614</v>
+      </c>
+      <c r="D213">
+        <v>5</v>
+      </c>
+      <c r="E213" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B214" t="s">
+        <v>615</v>
+      </c>
+      <c r="C214" t="s">
+        <v>616</v>
+      </c>
+      <c r="D214">
+        <v>5</v>
+      </c>
+      <c r="E214" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B215" t="s">
+        <v>617</v>
+      </c>
+      <c r="C215" t="s">
+        <v>618</v>
+      </c>
+      <c r="D215">
+        <v>5</v>
+      </c>
+      <c r="E215" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B216" t="s">
+        <v>619</v>
+      </c>
+      <c r="C216" t="s">
+        <v>620</v>
+      </c>
+      <c r="D216">
+        <v>5</v>
+      </c>
+      <c r="E216" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B217" t="s">
+        <v>621</v>
+      </c>
+      <c r="C217" t="s">
+        <v>622</v>
+      </c>
+      <c r="D217">
+        <v>5</v>
+      </c>
+      <c r="E217" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B218" t="s">
+        <v>623</v>
+      </c>
+      <c r="C218" t="s">
+        <v>624</v>
+      </c>
+      <c r="D218">
+        <v>5</v>
+      </c>
+      <c r="E218" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B219" t="s">
+        <v>625</v>
+      </c>
+      <c r="C219" t="s">
+        <v>626</v>
+      </c>
+      <c r="D219">
+        <v>5</v>
+      </c>
+      <c r="E219" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B220" t="s">
+        <v>627</v>
+      </c>
+      <c r="C220" t="s">
+        <v>628</v>
+      </c>
+      <c r="D220">
+        <v>5</v>
+      </c>
+      <c r="E220" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A221" t="s">
+        <v>629</v>
+      </c>
+      <c r="B221" t="s">
+        <v>630</v>
+      </c>
+      <c r="C221" t="s">
+        <v>631</v>
+      </c>
+      <c r="D221">
+        <v>5</v>
+      </c>
+      <c r="E221" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A222" t="s">
+        <v>629</v>
+      </c>
+      <c r="B222" t="s">
+        <v>632</v>
+      </c>
+      <c r="C222" t="s">
+        <v>633</v>
+      </c>
+      <c r="D222">
+        <v>5</v>
+      </c>
+      <c r="E222" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A223" t="s">
+        <v>629</v>
+      </c>
+      <c r="B223" t="s">
+        <v>634</v>
+      </c>
+      <c r="C223" t="s">
+        <v>635</v>
+      </c>
+      <c r="D223">
+        <v>5</v>
+      </c>
+      <c r="E223" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A224" t="s">
+        <v>629</v>
+      </c>
+      <c r="B224" t="s">
+        <v>636</v>
+      </c>
+      <c r="C224" t="s">
+        <v>637</v>
+      </c>
+      <c r="D224">
+        <v>5</v>
+      </c>
+      <c r="E224" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A225" t="s">
+        <v>629</v>
+      </c>
+      <c r="B225" t="s">
+        <v>638</v>
+      </c>
+      <c r="C225" t="s">
+        <v>639</v>
+      </c>
+      <c r="D225">
+        <v>5</v>
+      </c>
+      <c r="E225" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A226" t="s">
+        <v>629</v>
+      </c>
+      <c r="B226" t="s">
+        <v>640</v>
+      </c>
+      <c r="C226" t="s">
+        <v>641</v>
+      </c>
+      <c r="D226">
+        <v>5</v>
+      </c>
+      <c r="E226" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A227" t="s">
+        <v>629</v>
+      </c>
+      <c r="B227" t="s">
+        <v>642</v>
+      </c>
+      <c r="C227" t="s">
+        <v>643</v>
+      </c>
+      <c r="D227">
+        <v>5</v>
+      </c>
+      <c r="E227" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="229" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="230" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="231" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="232" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="233" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="234" spans="1:5" ht="16.5" customHeight="1">
+      <c r="B234" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="D234" s="1">
         <v>7</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E234" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="115" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="116" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="117" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="118" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="119" spans="1:5" ht="16.5" customHeight="1">
-      <c r="C119" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="16.5" customHeight="1">
-      <c r="C120" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="16.5" customHeight="1">
-      <c r="C121" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="16.5" customHeight="1">
-      <c r="C122" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="16.5" customHeight="1">
-      <c r="C123" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A124" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A125" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="16.5" customHeight="1">
-      <c r="C126" s="1" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="16.5" customHeight="1">
-      <c r="C127" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="16.5" customHeight="1">
-      <c r="C128" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="129" spans="3:3" ht="16.5" customHeight="1">
-      <c r="C129" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="130" spans="3:3" ht="16.5" customHeight="1">
-      <c r="C130" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="131" spans="3:3" ht="16.5" customHeight="1">
-      <c r="C131" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="132" spans="3:3" ht="16.5" customHeight="1">
-      <c r="C132" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="133" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="134" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="135" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="136" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="137" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="138" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="139" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="140" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="141" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="142" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="143" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="144" spans="3:3" ht="16.5" customHeight="1"/>
-    <row r="145" ht="16.5" customHeight="1"/>
-    <row r="146" ht="16.5" customHeight="1"/>
-    <row r="147" ht="16.5" customHeight="1"/>
-    <row r="148" ht="16.5" customHeight="1"/>
-    <row r="149" ht="16.5" customHeight="1"/>
-    <row r="150" ht="16.5" customHeight="1"/>
-    <row r="151" ht="16.5" customHeight="1"/>
-    <row r="152" ht="16.5" customHeight="1"/>
-    <row r="153" ht="16.5" customHeight="1"/>
-    <row r="154" ht="16.5" customHeight="1"/>
-    <row r="155" ht="16.5" customHeight="1"/>
-    <row r="156" ht="16.5" customHeight="1"/>
-    <row r="157" ht="16.5" customHeight="1"/>
-    <row r="158" ht="16.5" customHeight="1"/>
-    <row r="159" ht="16.5" customHeight="1"/>
-    <row r="160" ht="16.5" customHeight="1"/>
-    <row r="161" ht="16.5" customHeight="1"/>
-    <row r="162" ht="16.5" customHeight="1"/>
-    <row r="163" ht="16.5" customHeight="1"/>
-    <row r="164" ht="16.5" customHeight="1"/>
-    <row r="165" ht="16.5" customHeight="1"/>
-    <row r="166" ht="16.5" customHeight="1"/>
-    <row r="167" ht="16.5" customHeight="1"/>
-    <row r="168" ht="16.5" customHeight="1"/>
-    <row r="169" ht="16.5" customHeight="1"/>
-    <row r="170" ht="16.5" customHeight="1"/>
-    <row r="171" ht="16.5" customHeight="1"/>
-    <row r="172" ht="16.5" customHeight="1"/>
-    <row r="173" ht="16.5" customHeight="1"/>
-    <row r="174" ht="16.5" customHeight="1"/>
-    <row r="175" ht="16.5" customHeight="1"/>
-    <row r="176" ht="16.5" customHeight="1"/>
-    <row r="177" ht="16.5" customHeight="1"/>
-    <row r="178" ht="16.5" customHeight="1"/>
-    <row r="179" ht="16.5" customHeight="1"/>
-    <row r="180" ht="16.5" customHeight="1"/>
-    <row r="181" ht="16.5" customHeight="1"/>
-    <row r="182" ht="16.5" customHeight="1"/>
-    <row r="183" ht="16.5" customHeight="1"/>
-    <row r="184" ht="16.5" customHeight="1"/>
-    <row r="185" ht="16.5" customHeight="1"/>
-    <row r="186" ht="16.5" customHeight="1"/>
-    <row r="187" ht="16.5" customHeight="1"/>
-    <row r="188" ht="16.5" customHeight="1"/>
-    <row r="189" ht="16.5" customHeight="1"/>
-    <row r="190" ht="16.5" customHeight="1"/>
-    <row r="191" ht="16.5" customHeight="1"/>
-    <row r="192" ht="16.5" customHeight="1"/>
-    <row r="193" ht="16.5" customHeight="1"/>
-    <row r="194" ht="16.5" customHeight="1"/>
-    <row r="195" ht="16.5" customHeight="1"/>
-    <row r="196" ht="16.5" customHeight="1"/>
-    <row r="197" ht="16.5" customHeight="1"/>
-    <row r="198" ht="16.5" customHeight="1"/>
-    <row r="199" ht="16.5" customHeight="1"/>
-    <row r="200" ht="16.5" customHeight="1"/>
-    <row r="201" ht="16.5" customHeight="1"/>
-    <row r="202" ht="16.5" customHeight="1"/>
-    <row r="203" ht="16.5" customHeight="1"/>
-    <row r="204" ht="16.5" customHeight="1"/>
-    <row r="205" ht="16.5" customHeight="1"/>
-    <row r="206" ht="16.5" customHeight="1"/>
-    <row r="207" ht="16.5" customHeight="1"/>
-    <row r="208" ht="16.5" customHeight="1"/>
-    <row r="209" ht="16.5" customHeight="1"/>
-    <row r="210" ht="16.5" customHeight="1"/>
-    <row r="211" ht="16.5" customHeight="1"/>
-    <row r="212" ht="16.5" customHeight="1"/>
-    <row r="213" ht="16.5" customHeight="1"/>
-    <row r="214" ht="16.5" customHeight="1"/>
-    <row r="215" ht="16.5" customHeight="1"/>
-    <row r="216" ht="16.5" customHeight="1"/>
-    <row r="217" ht="16.5" customHeight="1"/>
-    <row r="218" ht="16.5" customHeight="1"/>
-    <row r="219" ht="16.5" customHeight="1"/>
-    <row r="220" ht="16.5" customHeight="1"/>
-    <row r="221" ht="16.5" customHeight="1"/>
-    <row r="222" ht="16.5" customHeight="1"/>
-    <row r="223" ht="16.5" customHeight="1"/>
-    <row r="224" ht="16.5" customHeight="1"/>
-    <row r="225" ht="16.5" customHeight="1"/>
-    <row r="226" ht="16.5" customHeight="1"/>
-    <row r="227" ht="16.5" customHeight="1"/>
-    <row r="228" ht="16.5" customHeight="1"/>
-    <row r="229" ht="16.5" customHeight="1"/>
-    <row r="230" ht="16.5" customHeight="1"/>
-    <row r="231" ht="16.5" customHeight="1"/>
-    <row r="232" ht="16.5" customHeight="1"/>
-    <row r="233" ht="16.5" customHeight="1"/>
-    <row r="234" ht="16.5" customHeight="1"/>
-    <row r="235" ht="16.5" customHeight="1"/>
-    <row r="236" ht="16.5" customHeight="1"/>
-    <row r="237" ht="16.5" customHeight="1"/>
-    <row r="238" ht="16.5" customHeight="1"/>
-    <row r="239" ht="16.5" customHeight="1"/>
-    <row r="240" ht="16.5" customHeight="1"/>
+    <row r="235" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="236" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="237" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="238" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="239" spans="1:5" ht="16.5" customHeight="1"/>
+    <row r="240" spans="1:5" ht="16.5" customHeight="1"/>
     <row r="241" ht="16.5" customHeight="1"/>
     <row r="242" ht="16.5" customHeight="1"/>
     <row r="243" ht="16.5" customHeight="1"/>
@@ -4734,7 +7005,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>351</v>
+        <v>646</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>10</v>
@@ -4754,7 +7025,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>352</v>
+        <v>647</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>14</v>
@@ -4774,7 +7045,7 @@
         <v>8</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>353</v>
+        <v>648</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>18</v>
@@ -4794,7 +7065,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>354</v>
+        <v>649</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>22</v>
@@ -4814,7 +7085,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>355</v>
+        <v>650</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>26</v>
@@ -4834,7 +7105,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>356</v>
+        <v>651</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>30</v>
@@ -4854,7 +7125,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>357</v>
+        <v>652</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>34</v>
@@ -4874,7 +7145,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>355</v>
+        <v>650</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="16.5" customHeight="1">
@@ -4891,7 +7162,7 @@
         <v>8</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>358</v>
+        <v>653</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>41</v>
@@ -4914,7 +7185,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>359</v>
+        <v>654</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>46</v>
@@ -4937,7 +7208,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>360</v>
+        <v>655</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>51</v>
@@ -4974,7 +7245,7 @@
         <v>59</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>361</v>
+        <v>656</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="16.5" customHeight="1">
@@ -4991,7 +7262,7 @@
         <v>8</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>362</v>
+        <v>657</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.5" customHeight="1">
@@ -5008,7 +7279,7 @@
         <v>8</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>363</v>
+        <v>658</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16.5" customHeight="1">
@@ -5025,7 +7296,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>364</v>
+        <v>659</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16.5" customHeight="1">
@@ -5061,13 +7332,13 @@
     </row>
     <row r="20" spans="1:7" ht="16.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>365</v>
+        <v>660</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>366</v>
+        <v>661</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -5078,13 +7349,13 @@
     </row>
     <row r="21" spans="1:7" ht="16.5" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>367</v>
+        <v>662</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>368</v>
+        <v>663</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -5096,10 +7367,10 @@
     <row r="22" spans="1:7" ht="16.5" customHeight="1"/>
     <row r="23" spans="1:7" ht="16.5" customHeight="1">
       <c r="B23" s="1" t="s">
-        <v>172</v>
+        <v>335</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>173</v>
+        <v>336</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -5110,10 +7381,10 @@
     </row>
     <row r="24" spans="1:7" ht="16.5" customHeight="1">
       <c r="B24" s="1" t="s">
-        <v>175</v>
+        <v>339</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>176</v>
+        <v>340</v>
       </c>
       <c r="D24" s="1">
         <v>3</v>
@@ -5124,10 +7395,10 @@
     </row>
     <row r="25" spans="1:7" ht="16.5" customHeight="1">
       <c r="B25" s="1" t="s">
-        <v>178</v>
+        <v>343</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>179</v>
+        <v>344</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -5138,10 +7409,10 @@
     </row>
     <row r="26" spans="1:7" ht="16.5" customHeight="1">
       <c r="B26" s="1" t="s">
-        <v>181</v>
+        <v>347</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>182</v>
+        <v>348</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
@@ -5152,10 +7423,10 @@
     </row>
     <row r="27" spans="1:7" ht="16.5" customHeight="1">
       <c r="B27" s="1" t="s">
-        <v>184</v>
+        <v>351</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>185</v>
+        <v>352</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
@@ -5166,10 +7437,10 @@
     </row>
     <row r="28" spans="1:7" ht="16.5" customHeight="1">
       <c r="B28" s="1" t="s">
-        <v>187</v>
+        <v>354</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>188</v>
+        <v>355</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -5178,15 +7449,15 @@
         <v>58</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>189</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="16.5" customHeight="1">
       <c r="B29" s="1" t="s">
-        <v>191</v>
+        <v>358</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>192</v>
+        <v>359</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -5197,10 +7468,10 @@
     </row>
     <row r="30" spans="1:7" ht="16.5" customHeight="1">
       <c r="B30" s="1" t="s">
-        <v>194</v>
+        <v>361</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>195</v>
+        <v>362</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -5211,10 +7482,10 @@
     </row>
     <row r="31" spans="1:7" ht="16.5" customHeight="1">
       <c r="B31" s="1" t="s">
-        <v>197</v>
+        <v>364</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -5225,10 +7496,10 @@
     </row>
     <row r="32" spans="1:7" ht="16.5" customHeight="1">
       <c r="B32" s="1" t="s">
-        <v>200</v>
+        <v>367</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>201</v>
+        <v>368</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -5239,10 +7510,10 @@
     </row>
     <row r="33" spans="2:6" ht="16.5" customHeight="1">
       <c r="B33" s="1" t="s">
-        <v>203</v>
+        <v>370</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>204</v>
+        <v>371</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -5253,10 +7524,10 @@
     </row>
     <row r="34" spans="2:6" ht="16.5" customHeight="1">
       <c r="B34" s="1" t="s">
-        <v>206</v>
+        <v>373</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>207</v>
+        <v>374</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -5267,10 +7538,10 @@
     </row>
     <row r="35" spans="2:6" ht="16.5" customHeight="1">
       <c r="B35" s="1" t="s">
-        <v>209</v>
+        <v>376</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>210</v>
+        <v>377</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
@@ -5279,15 +7550,15 @@
         <v>58</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>211</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" spans="2:6" ht="16.5" customHeight="1">
       <c r="B36" s="1" t="s">
-        <v>213</v>
+        <v>380</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>214</v>
+        <v>381</v>
       </c>
       <c r="D36" s="1">
         <v>3</v>
@@ -5298,10 +7569,10 @@
     </row>
     <row r="37" spans="2:6" ht="16.5" customHeight="1">
       <c r="B37" s="1" t="s">
-        <v>216</v>
+        <v>383</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>217</v>
+        <v>384</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
@@ -5312,10 +7583,10 @@
     </row>
     <row r="38" spans="2:6" ht="16.5" customHeight="1">
       <c r="B38" s="1" t="s">
-        <v>219</v>
+        <v>386</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>220</v>
+        <v>387</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
@@ -5324,15 +7595,15 @@
         <v>58</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>221</v>
+        <v>388</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="16.5" customHeight="1">
       <c r="B39" s="1" t="s">
-        <v>223</v>
+        <v>390</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>224</v>
+        <v>391</v>
       </c>
       <c r="D39" s="1">
         <v>3</v>
@@ -5343,10 +7614,10 @@
     </row>
     <row r="40" spans="2:6" ht="16.5" customHeight="1">
       <c r="B40" s="1" t="s">
-        <v>226</v>
+        <v>393</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>227</v>
+        <v>394</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -5355,15 +7626,15 @@
         <v>58</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>228</v>
+        <v>395</v>
       </c>
     </row>
     <row r="41" spans="2:6" ht="16.5" customHeight="1">
       <c r="B41" s="1" t="s">
-        <v>230</v>
+        <v>397</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>231</v>
+        <v>398</v>
       </c>
       <c r="D41" s="1">
         <v>3</v>
@@ -5372,15 +7643,15 @@
         <v>58</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>232</v>
+        <v>399</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="16.5" customHeight="1">
       <c r="B42" s="1" t="s">
-        <v>234</v>
+        <v>401</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>235</v>
+        <v>402</v>
       </c>
       <c r="D42" s="1">
         <v>3</v>
@@ -5389,15 +7660,15 @@
         <v>58</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>236</v>
+        <v>403</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="16.5" customHeight="1">
       <c r="B43" s="1" t="s">
-        <v>238</v>
+        <v>405</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>239</v>
+        <v>406</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -5408,10 +7679,10 @@
     </row>
     <row r="44" spans="2:6" ht="16.5" customHeight="1">
       <c r="B44" s="1" t="s">
-        <v>241</v>
+        <v>408</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>242</v>
+        <v>409</v>
       </c>
       <c r="D44" s="1">
         <v>3</v>
@@ -5423,10 +7694,10 @@
     <row r="45" spans="2:6" ht="16.5" customHeight="1"/>
     <row r="46" spans="2:6" ht="16.5" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>254</v>
+        <v>517</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>255</v>
+        <v>518</v>
       </c>
       <c r="D46" s="1">
         <v>4</v>
@@ -5435,15 +7706,15 @@
         <v>58</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>256</v>
+        <v>519</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="16.5" customHeight="1">
       <c r="B47" s="1" t="s">
-        <v>258</v>
+        <v>521</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>259</v>
+        <v>522</v>
       </c>
       <c r="D47" s="1">
         <v>4</v>
@@ -5452,15 +7723,15 @@
         <v>58</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>256</v>
+        <v>519</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="16.5" customHeight="1">
       <c r="B48" s="1" t="s">
-        <v>261</v>
+        <v>524</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>262</v>
+        <v>525</v>
       </c>
       <c r="D48" s="1">
         <v>4</v>
@@ -5469,15 +7740,15 @@
         <v>58</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>263</v>
+        <v>526</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="16.5" customHeight="1">
       <c r="B49" s="1" t="s">
-        <v>265</v>
+        <v>528</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>266</v>
+        <v>529</v>
       </c>
       <c r="D49" s="1">
         <v>4</v>
@@ -5488,10 +7759,10 @@
     </row>
     <row r="50" spans="2:6" ht="16.5" customHeight="1">
       <c r="B50" s="1" t="s">
-        <v>268</v>
+        <v>531</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>269</v>
+        <v>532</v>
       </c>
       <c r="D50" s="1">
         <v>4</v>
@@ -5500,15 +7771,15 @@
         <v>58</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>270</v>
+        <v>533</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="16.5" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>272</v>
+        <v>535</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>273</v>
+        <v>536</v>
       </c>
       <c r="D51" s="1">
         <v>4</v>
@@ -5517,15 +7788,15 @@
         <v>58</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>274</v>
+        <v>537</v>
       </c>
     </row>
     <row r="52" spans="2:6" ht="16.5" customHeight="1">
       <c r="B52" s="1" t="s">
-        <v>276</v>
+        <v>539</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>277</v>
+        <v>540</v>
       </c>
       <c r="D52" s="1">
         <v>4</v>
@@ -5534,15 +7805,15 @@
         <v>58</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>278</v>
+        <v>541</v>
       </c>
     </row>
     <row r="53" spans="2:6" ht="16.5" customHeight="1">
       <c r="B53" s="1" t="s">
-        <v>280</v>
+        <v>543</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>281</v>
+        <v>544</v>
       </c>
       <c r="D53" s="1">
         <v>4</v>
@@ -5551,15 +7822,15 @@
         <v>58</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>282</v>
+        <v>545</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="16.5" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>284</v>
+        <v>547</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>285</v>
+        <v>548</v>
       </c>
       <c r="D54" s="1">
         <v>4</v>
@@ -5570,10 +7841,10 @@
     </row>
     <row r="55" spans="2:6" ht="16.5" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>287</v>
+        <v>550</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>288</v>
+        <v>551</v>
       </c>
       <c r="D55" s="1">
         <v>4</v>
@@ -5584,10 +7855,10 @@
     </row>
     <row r="56" spans="2:6" ht="16.5" customHeight="1">
       <c r="B56" s="1" t="s">
-        <v>290</v>
+        <v>553</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>291</v>
+        <v>554</v>
       </c>
       <c r="D56" s="1">
         <v>4</v>
@@ -5598,10 +7869,10 @@
     </row>
     <row r="57" spans="2:6" ht="16.5" customHeight="1">
       <c r="B57" s="1" t="s">
-        <v>293</v>
+        <v>556</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>294</v>
+        <v>557</v>
       </c>
       <c r="D57" s="1">
         <v>4</v>
@@ -5612,10 +7883,10 @@
     </row>
     <row r="58" spans="2:6" ht="16.5" customHeight="1">
       <c r="B58" s="1" t="s">
-        <v>296</v>
+        <v>559</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>297</v>
+        <v>560</v>
       </c>
       <c r="D58" s="1">
         <v>4</v>
@@ -5624,15 +7895,15 @@
         <v>58</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>298</v>
+        <v>561</v>
       </c>
     </row>
     <row r="59" spans="2:6" ht="16.5" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>300</v>
+        <v>563</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>301</v>
+        <v>564</v>
       </c>
       <c r="D59" s="1">
         <v>4</v>
@@ -5641,15 +7912,15 @@
         <v>58</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>302</v>
+        <v>565</v>
       </c>
     </row>
     <row r="60" spans="2:6" ht="16.5" customHeight="1">
       <c r="B60" s="1" t="s">
-        <v>304</v>
+        <v>567</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>305</v>
+        <v>568</v>
       </c>
       <c r="D60" s="1">
         <v>4</v>
@@ -5660,10 +7931,10 @@
     </row>
     <row r="61" spans="2:6" ht="16.5" customHeight="1">
       <c r="B61" s="1" t="s">
-        <v>307</v>
+        <v>570</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>308</v>
+        <v>571</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
@@ -5674,10 +7945,10 @@
     </row>
     <row r="62" spans="2:6" ht="16.5" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>310</v>
+        <v>573</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>311</v>
+        <v>574</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
@@ -5688,10 +7959,10 @@
     </row>
     <row r="63" spans="2:6" ht="16.5" customHeight="1">
       <c r="B63" s="1" t="s">
-        <v>313</v>
+        <v>576</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>314</v>
+        <v>577</v>
       </c>
       <c r="D63" s="1">
         <v>4</v>
@@ -5702,10 +7973,10 @@
     </row>
     <row r="64" spans="2:6" ht="16.5" customHeight="1">
       <c r="B64" s="1" t="s">
-        <v>316</v>
+        <v>579</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>317</v>
+        <v>580</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
@@ -5716,10 +7987,10 @@
     </row>
     <row r="65" spans="2:5" ht="16.5" customHeight="1">
       <c r="B65" s="1" t="s">
-        <v>318</v>
+        <v>581</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>319</v>
+        <v>582</v>
       </c>
       <c r="D65" s="1">
         <v>4</v>
@@ -5730,10 +8001,10 @@
     </row>
     <row r="66" spans="2:5" ht="16.5" customHeight="1">
       <c r="B66" s="1" t="s">
-        <v>320</v>
+        <v>583</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>321</v>
+        <v>584</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
@@ -5744,10 +8015,10 @@
     </row>
     <row r="67" spans="2:5" ht="16.5" customHeight="1">
       <c r="B67" s="1" t="s">
-        <v>322</v>
+        <v>585</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>323</v>
+        <v>586</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
@@ -5759,10 +8030,10 @@
     <row r="68" spans="2:5" ht="16.5" customHeight="1"/>
     <row r="69" spans="2:5" ht="16.5" customHeight="1">
       <c r="B69" s="1" t="s">
-        <v>334</v>
+        <v>644</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>335</v>
+        <v>645</v>
       </c>
       <c r="D69" s="1">
         <v>7</v>
@@ -5782,73 +8053,73 @@
     <row r="78" spans="2:5" ht="16.5" customHeight="1"/>
     <row r="79" spans="2:5" ht="16.5" customHeight="1">
       <c r="C79" s="1" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="2:5" ht="16.5" customHeight="1">
       <c r="C80" s="1" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="16.5" customHeight="1">
       <c r="C81" s="1" t="s">
-        <v>259</v>
+        <v>522</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="16.5" customHeight="1">
       <c r="C82" s="1" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="16.5" customHeight="1">
       <c r="C83" s="1" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="16.5" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="16.5" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="16.5" customHeight="1">
       <c r="C86" s="1" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="16.5" customHeight="1">
       <c r="C87" s="1" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="16.5" customHeight="1">
       <c r="C88" s="1" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="16.5" customHeight="1">
       <c r="C89" s="1" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="16.5" customHeight="1">
       <c r="C90" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="16.5" customHeight="1">
       <c r="C91" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="16.5" customHeight="1">
@@ -6784,97 +9055,97 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>664</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>370</v>
+        <v>665</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>371</v>
+        <v>666</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>372</v>
+        <v>667</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>373</v>
+        <v>668</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>374</v>
+        <v>669</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>375</v>
+        <v>670</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>376</v>
+        <v>671</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>377</v>
+        <v>672</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>378</v>
+        <v>673</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>379</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>380</v>
+        <v>675</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>381</v>
+        <v>676</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>382</v>
+        <v>677</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>383</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>384</v>
+        <v>679</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>385</v>
+        <v>680</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>386</v>
+        <v>681</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>387</v>
+        <v>682</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>388</v>
+        <v>683</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>389</v>
+        <v>684</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>390</v>
+        <v>685</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>391</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>392</v>
+        <v>687</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>393</v>
+        <v>688</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>394</v>
+        <v>689</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>395</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1"/>
@@ -7907,7 +10178,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>396</v>
+        <v>691</v>
       </c>
       <c r="H1" s="2"/>
     </row>
@@ -7925,7 +10196,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>397</v>
+        <v>692</v>
       </c>
       <c r="N2" s="1"/>
       <c r="W2" s="2" t="s">
@@ -7946,7 +10217,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>398</v>
+        <v>693</v>
       </c>
       <c r="N3" s="1"/>
       <c r="W3" s="2" t="s">
@@ -7967,7 +10238,7 @@
         <v>8</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>399</v>
+        <v>694</v>
       </c>
       <c r="N4" s="1"/>
       <c r="W4" s="1" t="s">
@@ -7988,7 +10259,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>400</v>
+        <v>695</v>
       </c>
       <c r="N5" s="1"/>
       <c r="W5" s="2" t="s">
@@ -8009,7 +10280,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>401</v>
+        <v>696</v>
       </c>
       <c r="N6" s="1"/>
       <c r="W6" s="2" t="s">
@@ -8030,7 +10301,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>402</v>
+        <v>697</v>
       </c>
       <c r="N7" s="1"/>
       <c r="W7" s="2" t="s">
@@ -8051,7 +10322,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>403</v>
+        <v>698</v>
       </c>
       <c r="N8" s="1"/>
       <c r="W8" s="2" t="s">
@@ -8072,7 +10343,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>404</v>
+        <v>699</v>
       </c>
       <c r="N9" s="1"/>
     </row>
@@ -8090,7 +10361,7 @@
         <v>8</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>405</v>
+        <v>700</v>
       </c>
       <c r="N10" s="1"/>
     </row>
@@ -8108,7 +10379,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>406</v>
+        <v>701</v>
       </c>
       <c r="N11" s="1"/>
     </row>
@@ -8126,7 +10397,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>407</v>
+        <v>702</v>
       </c>
       <c r="N12" s="1"/>
       <c r="W12" s="1" t="s">
@@ -8287,16 +10558,16 @@
         <v>58</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>408</v>
+        <v>703</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16.5" customHeight="1"/>
     <row r="22" spans="1:14" ht="16.5" customHeight="1">
       <c r="B22" s="1" t="s">
-        <v>172</v>
+        <v>335</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>173</v>
+        <v>336</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -8305,15 +10576,15 @@
         <v>58</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>409</v>
+        <v>704</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="16.5" customHeight="1">
       <c r="B23" s="1" t="s">
-        <v>175</v>
+        <v>339</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>176</v>
+        <v>340</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -8322,16 +10593,16 @@
         <v>58</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>410</v>
+        <v>705</v>
       </c>
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="16.5" customHeight="1">
       <c r="B24" s="1" t="s">
-        <v>178</v>
+        <v>343</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>179</v>
+        <v>344</v>
       </c>
       <c r="D24" s="1">
         <v>3</v>
@@ -8340,16 +10611,16 @@
         <v>58</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>411</v>
+        <v>706</v>
       </c>
       <c r="N24" s="1"/>
     </row>
     <row r="25" spans="1:14" ht="16.5" customHeight="1">
       <c r="B25" s="1" t="s">
-        <v>181</v>
+        <v>347</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>182</v>
+        <v>348</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -8358,16 +10629,16 @@
         <v>58</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>183</v>
+        <v>349</v>
       </c>
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" ht="16.5" customHeight="1">
       <c r="B26" s="1" t="s">
-        <v>184</v>
+        <v>351</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>185</v>
+        <v>352</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
@@ -8376,16 +10647,16 @@
         <v>8</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>186</v>
+        <v>353</v>
       </c>
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" ht="16.5" customHeight="1">
       <c r="B27" s="1" t="s">
-        <v>187</v>
+        <v>354</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>188</v>
+        <v>355</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
@@ -8394,19 +10665,19 @@
         <v>58</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>189</v>
+        <v>356</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>190</v>
+        <v>357</v>
       </c>
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" ht="16.5" customHeight="1">
       <c r="B28" s="1" t="s">
-        <v>191</v>
+        <v>358</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>192</v>
+        <v>359</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -8415,16 +10686,16 @@
         <v>58</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>193</v>
+        <v>360</v>
       </c>
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" ht="16.5" customHeight="1">
       <c r="B29" s="1" t="s">
-        <v>194</v>
+        <v>361</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>195</v>
+        <v>362</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -8433,16 +10704,16 @@
         <v>58</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>196</v>
+        <v>363</v>
       </c>
       <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" ht="16.5" customHeight="1">
       <c r="B30" s="1" t="s">
-        <v>197</v>
+        <v>364</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -8451,16 +10722,16 @@
         <v>8</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>199</v>
+        <v>366</v>
       </c>
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" ht="16.5" customHeight="1">
       <c r="B31" s="1" t="s">
-        <v>200</v>
+        <v>367</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>201</v>
+        <v>368</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -8469,16 +10740,16 @@
         <v>8</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>202</v>
+        <v>369</v>
       </c>
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="16.5" customHeight="1">
       <c r="B32" s="1" t="s">
-        <v>203</v>
+        <v>370</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>204</v>
+        <v>371</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -8487,16 +10758,16 @@
         <v>8</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>205</v>
+        <v>372</v>
       </c>
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="2:14" ht="16.5" customHeight="1">
       <c r="B33" s="1" t="s">
-        <v>206</v>
+        <v>373</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>207</v>
+        <v>374</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -8505,16 +10776,16 @@
         <v>8</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>208</v>
+        <v>375</v>
       </c>
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="2:14" ht="16.5" customHeight="1">
       <c r="B34" s="1" t="s">
-        <v>209</v>
+        <v>376</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>210</v>
+        <v>377</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -8523,19 +10794,19 @@
         <v>58</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>211</v>
+        <v>378</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>212</v>
+        <v>379</v>
       </c>
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="2:14" ht="16.5" customHeight="1">
       <c r="B35" s="1" t="s">
-        <v>213</v>
+        <v>380</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>214</v>
+        <v>381</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
@@ -8544,16 +10815,16 @@
         <v>58</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>215</v>
+        <v>382</v>
       </c>
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="2:14" ht="16.5" customHeight="1">
       <c r="B36" s="1" t="s">
-        <v>216</v>
+        <v>383</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>217</v>
+        <v>384</v>
       </c>
       <c r="D36" s="1">
         <v>3</v>
@@ -8562,15 +10833,15 @@
         <v>58</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>129</v>
+        <v>707</v>
       </c>
     </row>
     <row r="37" spans="2:14" ht="16.5" customHeight="1">
       <c r="B37" s="1" t="s">
-        <v>219</v>
+        <v>386</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>220</v>
+        <v>387</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
@@ -8579,15 +10850,15 @@
         <v>58</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>221</v>
+        <v>388</v>
       </c>
     </row>
     <row r="38" spans="2:14" ht="16.5" customHeight="1">
       <c r="B38" s="1" t="s">
-        <v>223</v>
+        <v>390</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>224</v>
+        <v>391</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
@@ -8598,10 +10869,10 @@
     </row>
     <row r="39" spans="2:14" ht="16.5" customHeight="1">
       <c r="B39" s="1" t="s">
-        <v>226</v>
+        <v>393</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>227</v>
+        <v>394</v>
       </c>
       <c r="D39" s="1">
         <v>3</v>
@@ -8610,15 +10881,15 @@
         <v>58</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>228</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" spans="2:14" ht="16.5" customHeight="1">
       <c r="B40" s="1" t="s">
-        <v>230</v>
+        <v>397</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>231</v>
+        <v>398</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -8627,15 +10898,15 @@
         <v>58</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>232</v>
+        <v>399</v>
       </c>
     </row>
     <row r="41" spans="2:14" ht="16.5" customHeight="1">
       <c r="B41" s="1" t="s">
-        <v>234</v>
+        <v>401</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>235</v>
+        <v>402</v>
       </c>
       <c r="D41" s="1">
         <v>3</v>
@@ -8644,15 +10915,15 @@
         <v>58</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>236</v>
+        <v>403</v>
       </c>
     </row>
     <row r="42" spans="2:14" ht="16.5" customHeight="1">
       <c r="B42" s="1" t="s">
-        <v>238</v>
+        <v>405</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>239</v>
+        <v>406</v>
       </c>
       <c r="D42" s="1">
         <v>3</v>
@@ -8663,10 +10934,10 @@
     </row>
     <row r="43" spans="2:14" ht="16.5" customHeight="1">
       <c r="B43" s="1" t="s">
-        <v>241</v>
+        <v>408</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>242</v>
+        <v>409</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -8677,10 +10948,10 @@
     </row>
     <row r="44" spans="2:14" ht="16.5" customHeight="1">
       <c r="B44" s="1" t="s">
-        <v>244</v>
+        <v>411</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>412</v>
+        <v>708</v>
       </c>
       <c r="D44" s="1">
         <v>3</v>
@@ -8689,15 +10960,15 @@
         <v>58</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>413</v>
+        <v>709</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="16.5" customHeight="1">
       <c r="B45" t="s">
-        <v>247</v>
+        <v>414</v>
       </c>
       <c r="C45" t="s">
-        <v>250</v>
+        <v>418</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -8710,10 +10981,10 @@
     <row r="47" spans="2:14" ht="16.5" customHeight="1"/>
     <row r="48" spans="2:14" ht="16.5" customHeight="1">
       <c r="B48" s="1" t="s">
-        <v>254</v>
+        <v>517</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>255</v>
+        <v>518</v>
       </c>
       <c r="D48" s="1">
         <v>4</v>
@@ -8722,15 +10993,15 @@
         <v>58</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>256</v>
+        <v>519</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="16.5" customHeight="1">
       <c r="B49" s="1" t="s">
-        <v>258</v>
+        <v>521</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>259</v>
+        <v>522</v>
       </c>
       <c r="D49" s="1">
         <v>4</v>
@@ -8739,15 +11010,15 @@
         <v>58</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>256</v>
+        <v>519</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="16.5" customHeight="1">
       <c r="B50" s="1" t="s">
-        <v>261</v>
+        <v>524</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>262</v>
+        <v>525</v>
       </c>
       <c r="D50" s="1">
         <v>4</v>
@@ -8756,15 +11027,15 @@
         <v>58</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>263</v>
+        <v>526</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="16.5" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>265</v>
+        <v>528</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>266</v>
+        <v>529</v>
       </c>
       <c r="D51" s="1">
         <v>4</v>
@@ -8775,10 +11046,10 @@
     </row>
     <row r="52" spans="2:6" ht="16.5" customHeight="1">
       <c r="B52" s="1" t="s">
-        <v>268</v>
+        <v>531</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>269</v>
+        <v>532</v>
       </c>
       <c r="D52" s="1">
         <v>4</v>
@@ -8787,15 +11058,15 @@
         <v>58</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>270</v>
+        <v>533</v>
       </c>
     </row>
     <row r="53" spans="2:6" ht="16.5" customHeight="1">
       <c r="B53" s="1" t="s">
-        <v>272</v>
+        <v>535</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>273</v>
+        <v>536</v>
       </c>
       <c r="D53" s="1">
         <v>4</v>
@@ -8804,15 +11075,15 @@
         <v>58</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>274</v>
+        <v>537</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="16.5" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>276</v>
+        <v>539</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>277</v>
+        <v>540</v>
       </c>
       <c r="D54" s="1">
         <v>4</v>
@@ -8821,15 +11092,15 @@
         <v>58</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>278</v>
+        <v>541</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="16.5" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>280</v>
+        <v>543</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>281</v>
+        <v>544</v>
       </c>
       <c r="D55" s="1">
         <v>4</v>
@@ -8838,15 +11109,15 @@
         <v>58</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>282</v>
+        <v>545</v>
       </c>
     </row>
     <row r="56" spans="2:6" ht="16.5" customHeight="1">
       <c r="B56" s="1" t="s">
-        <v>284</v>
+        <v>547</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>285</v>
+        <v>548</v>
       </c>
       <c r="D56" s="1">
         <v>4</v>
@@ -8857,10 +11128,10 @@
     </row>
     <row r="57" spans="2:6" ht="16.5" customHeight="1">
       <c r="B57" s="1" t="s">
-        <v>287</v>
+        <v>550</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>288</v>
+        <v>551</v>
       </c>
       <c r="D57" s="1">
         <v>4</v>
@@ -8871,10 +11142,10 @@
     </row>
     <row r="58" spans="2:6" ht="16.5" customHeight="1">
       <c r="B58" s="1" t="s">
-        <v>290</v>
+        <v>553</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>291</v>
+        <v>554</v>
       </c>
       <c r="D58" s="1">
         <v>4</v>
@@ -8885,10 +11156,10 @@
     </row>
     <row r="59" spans="2:6" ht="16.5" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>293</v>
+        <v>556</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>294</v>
+        <v>557</v>
       </c>
       <c r="D59" s="1">
         <v>4</v>
@@ -8899,10 +11170,10 @@
     </row>
     <row r="60" spans="2:6" ht="16.5" customHeight="1">
       <c r="B60" s="1" t="s">
-        <v>296</v>
+        <v>559</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>297</v>
+        <v>560</v>
       </c>
       <c r="D60" s="1">
         <v>4</v>
@@ -8911,15 +11182,15 @@
         <v>58</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>298</v>
+        <v>561</v>
       </c>
     </row>
     <row r="61" spans="2:6" ht="16.5" customHeight="1">
       <c r="B61" s="1" t="s">
-        <v>300</v>
+        <v>563</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>301</v>
+        <v>564</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
@@ -8928,15 +11199,15 @@
         <v>58</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>302</v>
+        <v>565</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="16.5" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>304</v>
+        <v>567</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>305</v>
+        <v>568</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
@@ -8947,10 +11218,10 @@
     </row>
     <row r="63" spans="2:6" ht="16.5" customHeight="1">
       <c r="B63" s="1" t="s">
-        <v>307</v>
+        <v>570</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>308</v>
+        <v>571</v>
       </c>
       <c r="D63" s="1">
         <v>4</v>
@@ -8961,10 +11232,10 @@
     </row>
     <row r="64" spans="2:6" ht="16.5" customHeight="1">
       <c r="B64" s="1" t="s">
-        <v>310</v>
+        <v>573</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>311</v>
+        <v>574</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
@@ -8975,10 +11246,10 @@
     </row>
     <row r="65" spans="2:7" ht="16.5" customHeight="1">
       <c r="B65" s="1" t="s">
-        <v>313</v>
+        <v>576</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>314</v>
+        <v>577</v>
       </c>
       <c r="D65" s="1">
         <v>4</v>
@@ -8989,10 +11260,10 @@
     </row>
     <row r="66" spans="2:7" ht="16.5" customHeight="1">
       <c r="B66" s="1" t="s">
-        <v>316</v>
+        <v>579</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>317</v>
+        <v>580</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
@@ -9003,10 +11274,10 @@
     </row>
     <row r="67" spans="2:7" ht="16.5" customHeight="1">
       <c r="B67" s="1" t="s">
-        <v>318</v>
+        <v>581</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>319</v>
+        <v>582</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
@@ -9017,10 +11288,10 @@
     </row>
     <row r="68" spans="2:7" ht="16.5" customHeight="1">
       <c r="B68" s="1" t="s">
-        <v>320</v>
+        <v>583</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>321</v>
+        <v>584</v>
       </c>
       <c r="D68" s="1">
         <v>4</v>
@@ -9031,10 +11302,10 @@
     </row>
     <row r="69" spans="2:7" ht="16.5" customHeight="1">
       <c r="B69" s="1" t="s">
-        <v>322</v>
+        <v>585</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>323</v>
+        <v>586</v>
       </c>
       <c r="D69" s="1">
         <v>4</v>
@@ -9045,10 +11316,10 @@
     </row>
     <row r="70" spans="2:7" ht="16.5" customHeight="1">
       <c r="B70" s="1" t="s">
-        <v>324</v>
+        <v>587</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>325</v>
+        <v>588</v>
       </c>
       <c r="D70" s="1">
         <v>4</v>
@@ -9057,15 +11328,15 @@
         <v>8</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>414</v>
+        <v>710</v>
       </c>
     </row>
     <row r="71" spans="2:7" ht="16.5" customHeight="1">
       <c r="B71" s="1" t="s">
-        <v>327</v>
+        <v>590</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>328</v>
+        <v>591</v>
       </c>
       <c r="D71" s="1">
         <v>4</v>
@@ -9074,7 +11345,7 @@
         <v>8</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>415</v>
+        <v>711</v>
       </c>
     </row>
     <row r="72" spans="2:7" ht="16.5" customHeight="1">
@@ -9082,10 +11353,10 @@
     </row>
     <row r="73" spans="2:7" ht="16.5" customHeight="1">
       <c r="B73" s="1" t="s">
-        <v>334</v>
+        <v>644</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>335</v>
+        <v>645</v>
       </c>
       <c r="D73" s="1">
         <v>7</v>
@@ -9101,73 +11372,73 @@
     <row r="78" spans="2:7" ht="16.5" customHeight="1"/>
     <row r="79" spans="2:7" ht="16.5" customHeight="1">
       <c r="C79" s="1" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="2:7" ht="16.5" customHeight="1">
       <c r="C80" s="1" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="16.5" customHeight="1">
       <c r="C81" s="1" t="s">
-        <v>259</v>
+        <v>522</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="16.5" customHeight="1">
       <c r="C82" s="1" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="16.5" customHeight="1">
       <c r="C83" s="1" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="16.5" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="16.5" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="16.5" customHeight="1">
       <c r="C86" s="1" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="16.5" customHeight="1">
       <c r="C87" s="1" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="16.5" customHeight="1">
       <c r="C88" s="1" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="16.5" customHeight="1">
       <c r="C89" s="1" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="16.5" customHeight="1">
       <c r="C90" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="16.5" customHeight="1">
       <c r="C91" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="16.5" customHeight="1">
